--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
@@ -19,7 +19,6 @@
     <sheet sheetId="13" name="Approvals" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="Skills" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="Hand-overs" state="visible" r:id="rId18"/>
-    <sheet sheetId="16" name="Adapted this cycle" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -78,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7142" uniqueCount="1960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7082" uniqueCount="1929">
   <si>
     <t>Metric</t>
   </si>
@@ -221,7 +220,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T16:15:41.806Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T16:44:31.652Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -5658,7 +5657,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-11T16:15:43.264Z</t>
+    <t>2026-10-11T16:44:33.033Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5670,7 +5669,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-11T16:15:43.319Z</t>
+    <t>2026-10-11T16:44:33.075Z</t>
   </si>
   <si>
     <t>23 requirements, 29 test cases, 18 scripts merged: BL-2 v1 -&gt; v2</t>
@@ -5932,99 +5931,6 @@
   </si>
   <si>
     <t>cycleReport: delivered; comparison: delivered; testCaseExport: delivered</t>
-  </si>
-  <si>
-    <t>Lesson applied</t>
-  </si>
-  <si>
-    <t>risk-based priority</t>
-  </si>
-  <si>
-    <t>REQ-020 tested at High priority: defect history - DEF-009 on story AQPI-4</t>
-  </si>
-  <si>
-    <t>REQ-021 tested at High priority: defect history - DEF-009 on story AQPI-4</t>
-  </si>
-  <si>
-    <t>REQ-022 tested at High priority: defect history - DEF-009 on story AQPI-4</t>
-  </si>
-  <si>
-    <t>REQ-024 tested at High priority: defect history - DEF-009 on story AQPI-4</t>
-  </si>
-  <si>
-    <t>REQ-057 tested at High priority: defect history - DEF-007 on story AQPI-17</t>
-  </si>
-  <si>
-    <t>REQ-058 tested at High priority: defect history - DEF-007 on story AQPI-17</t>
-  </si>
-  <si>
-    <t>REQ-059 tested at High priority: defect history - DEF-007 on story AQPI-17</t>
-  </si>
-  <si>
-    <t>REQ-060 tested at High priority: defect history - DEF-007 on story AQPI-17</t>
-  </si>
-  <si>
-    <t>REQ-061 tested at High priority: defect history - DEF-007 on story AQPI-17</t>
-  </si>
-  <si>
-    <t>REQ-074 tested at High priority: defect history - DEF-008 on story AQPI-21</t>
-  </si>
-  <si>
-    <t>REQ-075 tested at High priority: defect history - DEF-008 on story AQPI-21</t>
-  </si>
-  <si>
-    <t>REQ-076 tested at High priority: defect history - DEF-008 on story AQPI-21</t>
-  </si>
-  <si>
-    <t>REQ-077 tested at High priority: defect history - DEF-008 on story AQPI-21</t>
-  </si>
-  <si>
-    <t>REQ-078 tested at High priority: defect history - DEF-008 on story AQPI-21</t>
-  </si>
-  <si>
-    <t>REQ-079 tested at High priority: defect history - DEF-008 on story AQPI-21</t>
-  </si>
-  <si>
-    <t>REQ-113 tested at High priority: defect history - DEF-007 (CYC-2) on this requirement</t>
-  </si>
-  <si>
-    <t>REQ-115 tested at High priority: defect history - DEF-008 (CYC-2) on this requirement</t>
-  </si>
-  <si>
-    <t>REQ-117 tested at High priority: defect history - DEF-009 (CYC-2) on this requirement</t>
-  </si>
-  <si>
-    <t>REQ-118 tested at High priority: defect history - DEF-009 on story AQPI-4</t>
-  </si>
-  <si>
-    <t>REQ-129 tested at High priority: defect history - DEF-001, DEF-004 on story AQPI-8</t>
-  </si>
-  <si>
-    <t>REQ-130 tested at High priority: defect history - DEF-001, DEF-004 on story AQPI-8</t>
-  </si>
-  <si>
-    <t>REQ-131 tested at High priority: defect history - DEF-001, DEF-004 on story AQPI-8</t>
-  </si>
-  <si>
-    <t>REQ-132 tested at High priority: defect history - DEF-001, DEF-004 on story AQPI-8</t>
-  </si>
-  <si>
-    <t>REQ-133 tested at High priority: defect history - DEF-002, DEF-005 on story AQPI-13</t>
-  </si>
-  <si>
-    <t>REQ-134 tested at High priority: defect history - DEF-002, DEF-005 on story AQPI-13</t>
-  </si>
-  <si>
-    <t>REQ-135 tested at High priority: defect history - DEF-002, DEF-005 on story AQPI-13</t>
-  </si>
-  <si>
-    <t>REQ-136 tested at High priority: defect history - DEF-003, DEF-006 on story AQPI-22</t>
-  </si>
-  <si>
-    <t>REQ-137 tested at High priority: defect history - DEF-003, DEF-006 on story AQPI-22</t>
-  </si>
-  <si>
-    <t>REQ-138 tested at High priority: defect history - DEF-003, DEF-006 on story AQPI-22</t>
   </si>
 </sst>
 </file>
@@ -14474,261 +14380,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1929</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1833</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1933</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1934</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1935</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1938</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1939</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
@@ -21056,7 +20707,7 @@
         <v>776</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>686</v>
@@ -21103,7 +20754,7 @@
         <v>783</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>686</v>
@@ -21150,7 +20801,7 @@
         <v>159</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>686</v>
@@ -21197,7 +20848,7 @@
         <v>167</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>686</v>
@@ -22748,7 +22399,7 @@
         <v>308</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>686</v>
@@ -22795,7 +22446,7 @@
         <v>312</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>686</v>
@@ -22842,7 +22493,7 @@
         <v>316</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>686</v>
@@ -22889,7 +22540,7 @@
         <v>320</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>686</v>
@@ -23735,7 +23386,7 @@
         <v>1068</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>686</v>
@@ -23782,7 +23433,7 @@
         <v>387</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>686</v>
@@ -23829,7 +23480,7 @@
         <v>391</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>686</v>
@@ -23876,7 +23527,7 @@
         <v>395</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>686</v>
@@ -25427,7 +25078,7 @@
         <v>1231</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>686</v>
@@ -25474,7 +25125,7 @@
         <v>1231</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>686</v>
@@ -25521,7 +25172,7 @@
         <v>1241</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>686</v>
@@ -25756,7 +25407,7 @@
         <v>1247</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>686</v>
@@ -25803,7 +25454,7 @@
         <v>1279</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>686</v>
@@ -25850,7 +25501,7 @@
         <v>1285</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>686</v>
@@ -25897,7 +25548,7 @@
         <v>1291</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>686</v>
@@ -25944,7 +25595,7 @@
         <v>1247</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>686</v>
@@ -25991,7 +25642,7 @@
         <v>1303</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>686</v>
@@ -26602,7 +26253,7 @@
         <v>1376</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>686</v>
@@ -26649,7 +26300,7 @@
         <v>1382</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>686</v>
@@ -26696,7 +26347,7 @@
         <v>1388</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>686</v>
@@ -26743,7 +26394,7 @@
         <v>632</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>686</v>
@@ -26790,7 +26441,7 @@
         <v>1397</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>686</v>
@@ -26837,7 +26488,7 @@
         <v>641</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="I140" s="5" t="s">
         <v>686</v>
@@ -26884,7 +26535,7 @@
         <v>1407</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I141" s="5" t="s">
         <v>686</v>
@@ -26931,7 +26582,7 @@
         <v>1413</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I142" s="5" t="s">
         <v>686</v>
@@ -26978,7 +26629,7 @@
         <v>1419</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>686</v>
@@ -27025,7 +26676,7 @@
         <v>1424</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I144" s="5" t="s">
         <v>686</v>
@@ -27072,7 +26723,7 @@
         <v>1430</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
       <c r="I145" s="5" t="s">
         <v>686</v>
@@ -27155,7 +26806,7 @@
         <v>1437</v>
       </c>
       <c r="E2" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -27279,7 +26930,7 @@
         <v>1437</v>
       </c>
       <c r="E8" s="2">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -27298,7 +26949,7 @@
         <v>1437</v>
       </c>
       <c r="E9" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -27317,7 +26968,7 @@
         <v>1437</v>
       </c>
       <c r="E10" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -27336,7 +26987,7 @@
         <v>1437</v>
       </c>
       <c r="E11" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -27355,7 +27006,7 @@
         <v>1437</v>
       </c>
       <c r="E12" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -27374,7 +27025,7 @@
         <v>1437</v>
       </c>
       <c r="E13" s="2">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -27456,7 +27107,7 @@
         <v>1437</v>
       </c>
       <c r="E17" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -27475,7 +27126,7 @@
         <v>1437</v>
       </c>
       <c r="E18" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -27536,7 +27187,7 @@
         <v>1437</v>
       </c>
       <c r="E21" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -27576,7 +27227,7 @@
         <v>1437</v>
       </c>
       <c r="E23" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -27614,7 +27265,7 @@
         <v>1437</v>
       </c>
       <c r="E25" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -27652,7 +27303,7 @@
         <v>1437</v>
       </c>
       <c r="E27" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -27671,7 +27322,7 @@
         <v>1437</v>
       </c>
       <c r="E28" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -27690,7 +27341,7 @@
         <v>1437</v>
       </c>
       <c r="E29" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -27751,7 +27402,7 @@
         <v>1437</v>
       </c>
       <c r="E32" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -27791,7 +27442,7 @@
         <v>1437</v>
       </c>
       <c r="E34" s="2">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -27810,7 +27461,7 @@
         <v>1437</v>
       </c>
       <c r="E35" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -27913,7 +27564,7 @@
         <v>1437</v>
       </c>
       <c r="E40" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -27932,7 +27583,7 @@
         <v>1437</v>
       </c>
       <c r="E41" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -27951,7 +27602,7 @@
         <v>1437</v>
       </c>
       <c r="E42" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -27970,7 +27621,7 @@
         <v>1437</v>
       </c>
       <c r="E43" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -28094,7 +27745,7 @@
         <v>1437</v>
       </c>
       <c r="E49" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -28113,7 +27764,7 @@
         <v>1437</v>
       </c>
       <c r="E50" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -28153,7 +27804,7 @@
         <v>1437</v>
       </c>
       <c r="E52" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -28256,7 +27907,7 @@
         <v>1437</v>
       </c>
       <c r="E57" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -28275,7 +27926,7 @@
         <v>1437</v>
       </c>
       <c r="E58" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -28294,7 +27945,7 @@
         <v>1437</v>
       </c>
       <c r="E59" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -28355,7 +28006,7 @@
         <v>1437</v>
       </c>
       <c r="E62" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -28374,7 +28025,7 @@
         <v>1437</v>
       </c>
       <c r="E63" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -28433,7 +28084,7 @@
         <v>1437</v>
       </c>
       <c r="E66" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -28452,7 +28103,7 @@
         <v>1437</v>
       </c>
       <c r="E67" s="2">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -28471,7 +28122,7 @@
         <v>1437</v>
       </c>
       <c r="E68" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -28490,7 +28141,7 @@
         <v>1437</v>
       </c>
       <c r="E69" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -28551,7 +28202,7 @@
         <v>1437</v>
       </c>
       <c r="E72" s="2">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -28570,7 +28221,7 @@
         <v>1437</v>
       </c>
       <c r="E73" s="2">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -28589,7 +28240,7 @@
         <v>1437</v>
       </c>
       <c r="E74" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -28671,7 +28322,7 @@
         <v>1437</v>
       </c>
       <c r="E78" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -28690,7 +28341,7 @@
         <v>1437</v>
       </c>
       <c r="E79" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -28730,7 +28381,7 @@
         <v>1437</v>
       </c>
       <c r="E81" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -28770,7 +28421,7 @@
         <v>1437</v>
       </c>
       <c r="E83" s="2">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -28852,7 +28503,7 @@
         <v>1437</v>
       </c>
       <c r="E87" s="2">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -28976,7 +28627,7 @@
         <v>1437</v>
       </c>
       <c r="E93" s="2">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -29016,7 +28667,7 @@
         <v>1437</v>
       </c>
       <c r="E95" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -29161,7 +28812,7 @@
         <v>1437</v>
       </c>
       <c r="E102" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -29262,7 +28913,7 @@
         <v>1437</v>
       </c>
       <c r="E107" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -29281,7 +28932,7 @@
         <v>1440</v>
       </c>
       <c r="E108" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -29300,7 +28951,7 @@
         <v>1437</v>
       </c>
       <c r="E109" s="2">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -29319,7 +28970,7 @@
         <v>1437</v>
       </c>
       <c r="E110" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -29338,7 +28989,7 @@
         <v>1440</v>
       </c>
       <c r="E111" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -29357,7 +29008,7 @@
         <v>1437</v>
       </c>
       <c r="E112" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -29395,7 +29046,7 @@
         <v>1437</v>
       </c>
       <c r="E114" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -29414,7 +29065,7 @@
         <v>1437</v>
       </c>
       <c r="E115" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -29433,7 +29084,7 @@
         <v>1440</v>
       </c>
       <c r="E116" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -29452,7 +29103,7 @@
         <v>1437</v>
       </c>
       <c r="E117" s="2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -29471,7 +29122,7 @@
         <v>1437</v>
       </c>
       <c r="E118" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -29490,7 +29141,7 @@
         <v>1437</v>
       </c>
       <c r="E119" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -29509,7 +29160,7 @@
         <v>1437</v>
       </c>
       <c r="E120" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -29528,7 +29179,7 @@
         <v>1437</v>
       </c>
       <c r="E121" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -29547,7 +29198,7 @@
         <v>1437</v>
       </c>
       <c r="E122" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -29608,7 +29259,7 @@
         <v>1437</v>
       </c>
       <c r="E125" s="2">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -29627,7 +29278,7 @@
         <v>1437</v>
       </c>
       <c r="E126" s="2">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -29646,7 +29297,7 @@
         <v>1437</v>
       </c>
       <c r="E127" s="2">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -29665,7 +29316,7 @@
         <v>1437</v>
       </c>
       <c r="E128" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -29684,7 +29335,7 @@
         <v>1437</v>
       </c>
       <c r="E129" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
@@ -29703,7 +29354,7 @@
         <v>1437</v>
       </c>
       <c r="E130" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -29722,7 +29373,7 @@
         <v>1440</v>
       </c>
       <c r="E131" s="2">
-        <v>403</v>
+        <v>370</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
@@ -29741,7 +29392,7 @@
         <v>1437</v>
       </c>
       <c r="E132" s="2">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -29760,7 +29411,7 @@
         <v>1437</v>
       </c>
       <c r="E133" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
@@ -29800,7 +29451,7 @@
         <v>1437</v>
       </c>
       <c r="E135" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -29819,7 +29470,7 @@
         <v>1437</v>
       </c>
       <c r="E136" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
@@ -29838,7 +29489,7 @@
         <v>1437</v>
       </c>
       <c r="E137" s="2">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
@@ -29878,7 +29529,7 @@
         <v>1437</v>
       </c>
       <c r="E139" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
@@ -29918,7 +29569,7 @@
         <v>1437</v>
       </c>
       <c r="E141" s="2">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -29937,7 +29588,7 @@
         <v>1437</v>
       </c>
       <c r="E142" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -29956,7 +29607,7 @@
         <v>1437</v>
       </c>
       <c r="E143" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -29975,7 +29626,7 @@
         <v>1437</v>
       </c>
       <c r="E144" s="2">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -29994,7 +29645,7 @@
         <v>1437</v>
       </c>
       <c r="E145" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
@@ -220,7 +220,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T16:44:31.652Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T17:07:02.366Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -5657,7 +5657,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-11T16:44:33.033Z</t>
+    <t>2026-10-11T17:07:03.754Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5669,7 +5669,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-11T16:44:33.075Z</t>
+    <t>2026-10-11T17:07:03.796Z</t>
   </si>
   <si>
     <t>23 requirements, 29 test cases, 18 scripts merged: BL-2 v1 -&gt; v2</t>
@@ -26806,7 +26806,7 @@
         <v>1437</v>
       </c>
       <c r="E2" s="2">
-        <v>525</v>
+        <v>566</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -26930,7 +26930,7 @@
         <v>1437</v>
       </c>
       <c r="E8" s="2">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -26949,7 +26949,7 @@
         <v>1437</v>
       </c>
       <c r="E9" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -26968,7 +26968,7 @@
         <v>1437</v>
       </c>
       <c r="E10" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -26987,7 +26987,7 @@
         <v>1437</v>
       </c>
       <c r="E11" s="2">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -27006,7 +27006,7 @@
         <v>1437</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -27025,7 +27025,7 @@
         <v>1437</v>
       </c>
       <c r="E13" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -27107,7 +27107,7 @@
         <v>1437</v>
       </c>
       <c r="E17" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -27187,7 +27187,7 @@
         <v>1437</v>
       </c>
       <c r="E21" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -27227,7 +27227,7 @@
         <v>1437</v>
       </c>
       <c r="E23" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -27246,7 +27246,7 @@
         <v>1437</v>
       </c>
       <c r="E24" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -27284,7 +27284,7 @@
         <v>1437</v>
       </c>
       <c r="E26" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -27303,7 +27303,7 @@
         <v>1437</v>
       </c>
       <c r="E27" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -27322,7 +27322,7 @@
         <v>1437</v>
       </c>
       <c r="E28" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -27341,7 +27341,7 @@
         <v>1437</v>
       </c>
       <c r="E29" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -27402,7 +27402,7 @@
         <v>1437</v>
       </c>
       <c r="E32" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -27442,7 +27442,7 @@
         <v>1437</v>
       </c>
       <c r="E34" s="2">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -27461,7 +27461,7 @@
         <v>1437</v>
       </c>
       <c r="E35" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -27564,7 +27564,7 @@
         <v>1437</v>
       </c>
       <c r="E40" s="2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -27583,7 +27583,7 @@
         <v>1437</v>
       </c>
       <c r="E41" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -27602,7 +27602,7 @@
         <v>1437</v>
       </c>
       <c r="E42" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -27621,7 +27621,7 @@
         <v>1437</v>
       </c>
       <c r="E43" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -27745,7 +27745,7 @@
         <v>1437</v>
       </c>
       <c r="E49" s="2">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -27764,7 +27764,7 @@
         <v>1437</v>
       </c>
       <c r="E50" s="2">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -27804,7 +27804,7 @@
         <v>1437</v>
       </c>
       <c r="E52" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -27907,7 +27907,7 @@
         <v>1437</v>
       </c>
       <c r="E57" s="2">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -27926,7 +27926,7 @@
         <v>1437</v>
       </c>
       <c r="E58" s="2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -27945,7 +27945,7 @@
         <v>1437</v>
       </c>
       <c r="E59" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -28006,7 +28006,7 @@
         <v>1437</v>
       </c>
       <c r="E62" s="2">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -28025,7 +28025,7 @@
         <v>1437</v>
       </c>
       <c r="E63" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -28044,7 +28044,7 @@
         <v>1437</v>
       </c>
       <c r="E64" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -28084,7 +28084,7 @@
         <v>1437</v>
       </c>
       <c r="E66" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -28103,7 +28103,7 @@
         <v>1437</v>
       </c>
       <c r="E67" s="2">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -28122,7 +28122,7 @@
         <v>1437</v>
       </c>
       <c r="E68" s="2">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -28202,7 +28202,7 @@
         <v>1437</v>
       </c>
       <c r="E72" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -28221,7 +28221,7 @@
         <v>1437</v>
       </c>
       <c r="E73" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -28240,7 +28240,7 @@
         <v>1437</v>
       </c>
       <c r="E74" s="2">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -28322,7 +28322,7 @@
         <v>1437</v>
       </c>
       <c r="E78" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -28341,7 +28341,7 @@
         <v>1437</v>
       </c>
       <c r="E79" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -28381,7 +28381,7 @@
         <v>1437</v>
       </c>
       <c r="E81" s="2">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -28421,7 +28421,7 @@
         <v>1437</v>
       </c>
       <c r="E83" s="2">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -28503,7 +28503,7 @@
         <v>1437</v>
       </c>
       <c r="E87" s="2">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -28627,7 +28627,7 @@
         <v>1437</v>
       </c>
       <c r="E93" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -28667,7 +28667,7 @@
         <v>1437</v>
       </c>
       <c r="E95" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -28812,7 +28812,7 @@
         <v>1437</v>
       </c>
       <c r="E102" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -28894,7 +28894,7 @@
         <v>1437</v>
       </c>
       <c r="E106" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -28913,7 +28913,7 @@
         <v>1437</v>
       </c>
       <c r="E107" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -28932,7 +28932,7 @@
         <v>1440</v>
       </c>
       <c r="E108" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -28951,7 +28951,7 @@
         <v>1437</v>
       </c>
       <c r="E109" s="2">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -28970,7 +28970,7 @@
         <v>1437</v>
       </c>
       <c r="E110" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -28989,7 +28989,7 @@
         <v>1440</v>
       </c>
       <c r="E111" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -29008,7 +29008,7 @@
         <v>1437</v>
       </c>
       <c r="E112" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -29027,7 +29027,7 @@
         <v>1437</v>
       </c>
       <c r="E113" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -29046,7 +29046,7 @@
         <v>1437</v>
       </c>
       <c r="E114" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -29065,7 +29065,7 @@
         <v>1437</v>
       </c>
       <c r="E115" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -29084,7 +29084,7 @@
         <v>1440</v>
       </c>
       <c r="E116" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -29103,7 +29103,7 @@
         <v>1437</v>
       </c>
       <c r="E117" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -29122,7 +29122,7 @@
         <v>1437</v>
       </c>
       <c r="E118" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -29141,7 +29141,7 @@
         <v>1437</v>
       </c>
       <c r="E119" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -29160,7 +29160,7 @@
         <v>1437</v>
       </c>
       <c r="E120" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -29179,7 +29179,7 @@
         <v>1437</v>
       </c>
       <c r="E121" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -29198,7 +29198,7 @@
         <v>1437</v>
       </c>
       <c r="E122" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -29259,7 +29259,7 @@
         <v>1437</v>
       </c>
       <c r="E125" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -29297,7 +29297,7 @@
         <v>1437</v>
       </c>
       <c r="E127" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -29316,7 +29316,7 @@
         <v>1437</v>
       </c>
       <c r="E128" s="2">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -29335,7 +29335,7 @@
         <v>1437</v>
       </c>
       <c r="E129" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
@@ -29354,7 +29354,7 @@
         <v>1437</v>
       </c>
       <c r="E130" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -29373,7 +29373,7 @@
         <v>1440</v>
       </c>
       <c r="E131" s="2">
-        <v>370</v>
+        <v>421</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
@@ -29392,7 +29392,7 @@
         <v>1437</v>
       </c>
       <c r="E132" s="2">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -29411,7 +29411,7 @@
         <v>1437</v>
       </c>
       <c r="E133" s="2">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
@@ -29451,7 +29451,7 @@
         <v>1437</v>
       </c>
       <c r="E135" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -29470,7 +29470,7 @@
         <v>1437</v>
       </c>
       <c r="E136" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
@@ -29489,7 +29489,7 @@
         <v>1437</v>
       </c>
       <c r="E137" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
@@ -29529,7 +29529,7 @@
         <v>1437</v>
       </c>
       <c r="E139" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
@@ -29569,7 +29569,7 @@
         <v>1437</v>
       </c>
       <c r="E141" s="2">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -29607,7 +29607,7 @@
         <v>1437</v>
       </c>
       <c r="E143" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -29626,7 +29626,7 @@
         <v>1437</v>
       </c>
       <c r="E144" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -29645,7 +29645,7 @@
         <v>1437</v>
       </c>
       <c r="E145" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
@@ -139,7 +139,7 @@
     <t>{"functional":173,"automation":83,"regression":115,"non-functional":4}</t>
   </si>
   <si>
-    <t>Scripts</t>
+    <t>Automation scripts</t>
   </si>
   <si>
     <t>Executed (real)</t>
@@ -220,7 +220,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-11T17:07:02.366Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-12T01:35:20.908Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -5657,7 +5657,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-11T17:07:03.754Z</t>
+    <t>2026-10-12T01:35:22.376Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5669,7 +5669,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-11T17:07:03.796Z</t>
+    <t>2026-10-12T01:35:22.429Z</t>
   </si>
   <si>
     <t>23 requirements, 29 test cases, 18 scripts merged: BL-2 v1 -&gt; v2</t>
@@ -5807,7 +5807,7 @@
     <t>testing-functional</t>
   </si>
   <si>
-    <t>Functional testing</t>
+    <t>DQE testing (domain functional)</t>
   </si>
   <si>
     <t>Steers the design agents to cover every business rule and its boundaries through the service API.</t>
@@ -26806,7 +26806,7 @@
         <v>1437</v>
       </c>
       <c r="E2" s="2">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -26930,7 +26930,7 @@
         <v>1437</v>
       </c>
       <c r="E8" s="2">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -26949,7 +26949,7 @@
         <v>1437</v>
       </c>
       <c r="E9" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -26968,7 +26968,7 @@
         <v>1437</v>
       </c>
       <c r="E10" s="2">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -27006,7 +27006,7 @@
         <v>1437</v>
       </c>
       <c r="E12" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -27025,7 +27025,7 @@
         <v>1437</v>
       </c>
       <c r="E13" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -27107,7 +27107,7 @@
         <v>1437</v>
       </c>
       <c r="E17" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -27126,7 +27126,7 @@
         <v>1437</v>
       </c>
       <c r="E18" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -27187,7 +27187,7 @@
         <v>1437</v>
       </c>
       <c r="E21" s="2">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -27227,7 +27227,7 @@
         <v>1437</v>
       </c>
       <c r="E23" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -27246,7 +27246,7 @@
         <v>1437</v>
       </c>
       <c r="E24" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -27265,7 +27265,7 @@
         <v>1437</v>
       </c>
       <c r="E25" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -27284,7 +27284,7 @@
         <v>1437</v>
       </c>
       <c r="E26" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -27303,7 +27303,7 @@
         <v>1437</v>
       </c>
       <c r="E27" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -27322,7 +27322,7 @@
         <v>1437</v>
       </c>
       <c r="E28" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -27341,7 +27341,7 @@
         <v>1437</v>
       </c>
       <c r="E29" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -27402,7 +27402,7 @@
         <v>1437</v>
       </c>
       <c r="E32" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -27442,7 +27442,7 @@
         <v>1437</v>
       </c>
       <c r="E34" s="2">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -27461,7 +27461,7 @@
         <v>1437</v>
       </c>
       <c r="E35" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -27583,7 +27583,7 @@
         <v>1437</v>
       </c>
       <c r="E41" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -27602,7 +27602,7 @@
         <v>1437</v>
       </c>
       <c r="E42" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -27621,7 +27621,7 @@
         <v>1437</v>
       </c>
       <c r="E43" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -27745,7 +27745,7 @@
         <v>1437</v>
       </c>
       <c r="E49" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -27764,7 +27764,7 @@
         <v>1437</v>
       </c>
       <c r="E50" s="2">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -27804,7 +27804,7 @@
         <v>1437</v>
       </c>
       <c r="E52" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -27907,7 +27907,7 @@
         <v>1437</v>
       </c>
       <c r="E57" s="2">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -27926,7 +27926,7 @@
         <v>1437</v>
       </c>
       <c r="E58" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -27945,7 +27945,7 @@
         <v>1437</v>
       </c>
       <c r="E59" s="2">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -28006,7 +28006,7 @@
         <v>1437</v>
       </c>
       <c r="E62" s="2">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -28025,7 +28025,7 @@
         <v>1437</v>
       </c>
       <c r="E63" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -28044,7 +28044,7 @@
         <v>1437</v>
       </c>
       <c r="E64" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -28084,7 +28084,7 @@
         <v>1437</v>
       </c>
       <c r="E66" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -28103,7 +28103,7 @@
         <v>1437</v>
       </c>
       <c r="E67" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -28122,7 +28122,7 @@
         <v>1437</v>
       </c>
       <c r="E68" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -28141,7 +28141,7 @@
         <v>1437</v>
       </c>
       <c r="E69" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -28221,7 +28221,7 @@
         <v>1437</v>
       </c>
       <c r="E73" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -28240,7 +28240,7 @@
         <v>1437</v>
       </c>
       <c r="E74" s="2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -28322,7 +28322,7 @@
         <v>1437</v>
       </c>
       <c r="E78" s="2">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -28341,7 +28341,7 @@
         <v>1437</v>
       </c>
       <c r="E79" s="2">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -28381,7 +28381,7 @@
         <v>1437</v>
       </c>
       <c r="E81" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -28421,7 +28421,7 @@
         <v>1437</v>
       </c>
       <c r="E83" s="2">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -28503,7 +28503,7 @@
         <v>1437</v>
       </c>
       <c r="E87" s="2">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -28627,7 +28627,7 @@
         <v>1437</v>
       </c>
       <c r="E93" s="2">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -28667,7 +28667,7 @@
         <v>1437</v>
       </c>
       <c r="E95" s="2">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -28812,7 +28812,7 @@
         <v>1437</v>
       </c>
       <c r="E102" s="2">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -28894,7 +28894,7 @@
         <v>1437</v>
       </c>
       <c r="E106" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -28913,7 +28913,7 @@
         <v>1437</v>
       </c>
       <c r="E107" s="2">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -28932,7 +28932,7 @@
         <v>1440</v>
       </c>
       <c r="E108" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -28951,7 +28951,7 @@
         <v>1437</v>
       </c>
       <c r="E109" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -28989,7 +28989,7 @@
         <v>1440</v>
       </c>
       <c r="E111" s="2">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -29008,7 +29008,7 @@
         <v>1437</v>
       </c>
       <c r="E112" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -29027,7 +29027,7 @@
         <v>1437</v>
       </c>
       <c r="E113" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -29046,7 +29046,7 @@
         <v>1437</v>
       </c>
       <c r="E114" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -29065,7 +29065,7 @@
         <v>1437</v>
       </c>
       <c r="E115" s="2">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -29084,7 +29084,7 @@
         <v>1440</v>
       </c>
       <c r="E116" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -29141,7 +29141,7 @@
         <v>1437</v>
       </c>
       <c r="E119" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -29179,7 +29179,7 @@
         <v>1437</v>
       </c>
       <c r="E121" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -29198,7 +29198,7 @@
         <v>1437</v>
       </c>
       <c r="E122" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -29259,7 +29259,7 @@
         <v>1437</v>
       </c>
       <c r="E125" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -29278,7 +29278,7 @@
         <v>1437</v>
       </c>
       <c r="E126" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -29297,7 +29297,7 @@
         <v>1437</v>
       </c>
       <c r="E127" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -29316,7 +29316,7 @@
         <v>1437</v>
       </c>
       <c r="E128" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -29335,7 +29335,7 @@
         <v>1437</v>
       </c>
       <c r="E129" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
@@ -29354,7 +29354,7 @@
         <v>1437</v>
       </c>
       <c r="E130" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -29373,7 +29373,7 @@
         <v>1440</v>
       </c>
       <c r="E131" s="2">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
@@ -29392,7 +29392,7 @@
         <v>1437</v>
       </c>
       <c r="E132" s="2">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -29411,7 +29411,7 @@
         <v>1437</v>
       </c>
       <c r="E133" s="2">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
@@ -29451,7 +29451,7 @@
         <v>1437</v>
       </c>
       <c r="E135" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -29470,7 +29470,7 @@
         <v>1437</v>
       </c>
       <c r="E136" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
@@ -29489,7 +29489,7 @@
         <v>1437</v>
       </c>
       <c r="E137" s="2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
@@ -29529,7 +29529,7 @@
         <v>1437</v>
       </c>
       <c r="E139" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
@@ -29569,7 +29569,7 @@
         <v>1437</v>
       </c>
       <c r="E141" s="2">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -29588,7 +29588,7 @@
         <v>1437</v>
       </c>
       <c r="E142" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -29607,7 +29607,7 @@
         <v>1437</v>
       </c>
       <c r="E143" s="2">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -29626,7 +29626,7 @@
         <v>1437</v>
       </c>
       <c r="E144" s="2">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -29645,7 +29645,7 @@
         <v>1437</v>
       </c>
       <c r="E145" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7082" uniqueCount="1929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7072" uniqueCount="1920">
   <si>
     <t>Metric</t>
   </si>
@@ -169,7 +169,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 20 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 79 passed and 4 failed (pass rate 95.2%). 4 defect(s) were raised from real failures: DEF-007 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-008 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-010 A 15-night stay in Paris is rejected: returns 200 instead of 400; DEF-011 Operations can retry a failed confirmation e-mail 3 times; retry 4 is refused: returns 200 instead of 409.</t>
+    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 20 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 82 passed and 1 failed (pass rate 98.8%). 1 defect(s) were raised from real failures: DEF-010 Support staff see a masked e-mail and other callers are refused: failed.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -214,13 +214,13 @@
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44)</t>
+    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (fe1ce44) at 2026-10-12T01:35:20.908Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) at 2026-10-12T02:09:53.132Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3741,7 +3741,7 @@
     <t>Verify a change above 1% needs acknowledgement before checkout.</t>
   </si>
   <si>
-    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate rises 30% after the cart is created.</t>
+    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate is 200 when the cart is created and rises 30% to 260.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Create a cart
@@ -3767,7 +3767,7 @@
     <t>Verify a change within 1% is applied without blocking the guest.</t>
   </si>
   <si>
-    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate rises 0.5% after the cart is created.</t>
+    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate is 200 when the cart is created and rises 0.5% to 201.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Create a cart
@@ -4505,28 +4505,73 @@
     <t>AI likely cause</t>
   </si>
   <si>
+    <t>DEF-010</t>
+  </si>
+  <si>
+    <t>Support staff see a masked e-mail and other callers are refused: failed</t>
+  </si>
+  <si>
+    <t>not raised in Jira; linked to AQPI-19 in the platform</t>
+  </si>
+  <si>
+    <t>(see failing assertion)</t>
+  </si>
+  <si>
+    <t>Test timeout of 30000ms exceeded.</t>
+  </si>
+  <si>
+    <t>First seen</t>
+  </si>
+  <si>
+    <t>Retested in</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
+    <t>DEF-004</t>
+  </si>
+  <si>
+    <t>AQPI-8 4.2 Sort and filter hotel results: asked for in Jira but not implemented in the code</t>
+  </si>
+  <si>
+    <t>CYC-2</t>
+  </si>
+  <si>
+    <t>CYC-3</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>AQPI-8 is implemented in build demo/hotel-booking-platform-v2; 4 test(s) of the picked-up gap passed in CYC-3, so DEF-004 (gap from CYC-2) is closed.</t>
+  </si>
+  <si>
+    <t>DEF-005</t>
+  </si>
+  <si>
+    <t>AQPI-13 5.3 Explain and control personalization: asked for in Jira but not implemented in the code</t>
+  </si>
+  <si>
+    <t>AQPI-13 is implemented in build demo/hotel-booking-platform-v2; 2 test(s) of the picked-up gap passed in CYC-3, so DEF-005 (gap from CYC-2) is closed.</t>
+  </si>
+  <si>
+    <t>DEF-006</t>
+  </si>
+  <si>
+    <t>AQPI-22 7.4 Show booking outcome: asked for in Jira but not implemented in the code</t>
+  </si>
+  <si>
+    <t>AQPI-22 is implemented in build demo/hotel-booking-platform-v2; 3 test(s) of the picked-up gap passed in CYC-3, so DEF-006 (gap from CYC-2) is closed.</t>
+  </si>
+  <si>
     <t>DEF-007</t>
   </si>
   <si>
     <t>A price change within 1% does not need acknowledgement: returns true instead of false</t>
   </si>
   <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>not raised in Jira; linked to AQPI-17 in the platform</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>expect(rv.body.requiresAcknowledgement).toBe(false);</t>
-  </si>
-  <si>
-    <t>still open</t>
+    <t>Fixed in build demo/hotel-booking-platform-v2; TC-F-103 re-run in CYC-3 passed, so DEF-007 (first seen in CYC-2) is certified closed.</t>
   </si>
   <si>
     <t>DEF-008</t>
@@ -4535,88 +4580,7 @@
     <t>A key shorter than 8 characters is refused: returns 201 instead of 400</t>
   </si>
   <si>
-    <t>not raised in Jira; linked to AQPI-21 in the platform</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>expect(r.status).toBe(400);</t>
-  </si>
-  <si>
-    <t>DEF-010</t>
-  </si>
-  <si>
-    <t>A 15-night stay in Paris is rejected: returns 200 instead of 400</t>
-  </si>
-  <si>
-    <t>not raised in Jira; linked to AQPI-34 in the platform</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>DEF-011</t>
-  </si>
-  <si>
-    <t>Operations can retry a failed confirmation e-mail 3 times; retry 4 is refused: returns 200 instead of 409</t>
-  </si>
-  <si>
-    <t>not raised in Jira; linked to AQPI-25 in the platform</t>
-  </si>
-  <si>
-    <t>409</t>
-  </si>
-  <si>
-    <t>expect(over.status).toBe(409);</t>
-  </si>
-  <si>
-    <t>First seen</t>
-  </si>
-  <si>
-    <t>Retested in</t>
-  </si>
-  <si>
-    <t>Certification</t>
-  </si>
-  <si>
-    <t>DEF-004</t>
-  </si>
-  <si>
-    <t>AQPI-8 4.2 Sort and filter hotel results: asked for in Jira but not implemented in the code</t>
-  </si>
-  <si>
-    <t>CYC-2</t>
-  </si>
-  <si>
-    <t>CYC-3</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>AQPI-8 is implemented in build demo/hotel-booking-platform-v2; 4 test(s) of the picked-up gap passed in CYC-3, so DEF-004 (gap from CYC-2) is closed.</t>
-  </si>
-  <si>
-    <t>DEF-005</t>
-  </si>
-  <si>
-    <t>AQPI-13 5.3 Explain and control personalization: asked for in Jira but not implemented in the code</t>
-  </si>
-  <si>
-    <t>AQPI-13 is implemented in build demo/hotel-booking-platform-v2; 2 test(s) of the picked-up gap passed in CYC-3, so DEF-005 (gap from CYC-2) is closed.</t>
-  </si>
-  <si>
-    <t>DEF-006</t>
-  </si>
-  <si>
-    <t>AQPI-22 7.4 Show booking outcome: asked for in Jira but not implemented in the code</t>
-  </si>
-  <si>
-    <t>AQPI-22 is implemented in build demo/hotel-booking-platform-v2; 3 test(s) of the picked-up gap passed in CYC-3, so DEF-006 (gap from CYC-2) is closed.</t>
+    <t>Fixed in build demo/hotel-booking-platform-v2; TC-F-106 re-run in CYC-3 passed, so DEF-008 (first seen in CYC-2) is certified closed.</t>
   </si>
   <si>
     <t>DEF-009</t>
@@ -4667,7 +4631,7 @@
     <t>TC-F-007, TC-F-011, TC-F-110, TC-F-111</t>
   </si>
   <si>
-    <t>exercised - failing</t>
+    <t>exercised - passing</t>
   </si>
   <si>
     <t>stay.checkInOffsetDays</t>
@@ -4679,9 +4643,6 @@
     <t>TC-F-009, TC-F-116, TC-F-117, TC-F-121</t>
   </si>
   <si>
-    <t>exercised - passing</t>
-  </si>
-  <si>
     <t>stay.nights</t>
   </si>
   <si>
@@ -4826,111 +4787,111 @@
     <t>10.2 Limit Paris stays to 14 nights</t>
   </si>
   <si>
+    <t>10.3 Allow up to 5 confirmation resends</t>
+  </si>
+  <si>
+    <t>10.4 Cancel a reservation free of charge</t>
+  </si>
+  <si>
+    <t>AQPI-23</t>
+  </si>
+  <si>
+    <t>[Epic 6] Confirmation and Notifications</t>
+  </si>
+  <si>
+    <t>8.1 Generate confirmation message</t>
+  </si>
+  <si>
+    <t>8.2 Send and track confirmation email</t>
+  </si>
+  <si>
+    <t>8.3 Resend confirmation safely</t>
+  </si>
+  <si>
+    <t>8.4 Send a cancellation e-mail</t>
+  </si>
+  <si>
+    <t>initiative</t>
+  </si>
+  <si>
+    <t>baseline</t>
+  </si>
+  <si>
+    <t>[Initiative] Intelligent Hotel Shopping and Reservation Experience</t>
+  </si>
+  <si>
+    <t>AQPI-2</t>
+  </si>
+  <si>
+    <t>[Epic 1] Search and Availability</t>
+  </si>
+  <si>
+    <t>3.1 Search hotels by destination and date range</t>
+  </si>
+  <si>
+    <t>3.2 Validate occupancy and stay criteria</t>
+  </si>
+  <si>
+    <t>3.3 Handle unavailable or failed searches</t>
+  </si>
+  <si>
+    <t>AQPI-6</t>
+  </si>
+  <si>
+    <t>[Epic 2] Hotel Results and Selection</t>
+  </si>
+  <si>
+    <t>4.1 Display available hotels</t>
+  </si>
+  <si>
+    <t>4.2 Sort and filter hotel results</t>
+  </si>
+  <si>
+    <t>4.3 View hotel and room details</t>
+  </si>
+  <si>
+    <t>AQPI-10</t>
+  </si>
+  <si>
+    <t>[Epic 3] Personalized Ancillary Offers</t>
+  </si>
+  <si>
+    <t>5.1 Determine eligible ancillary offers</t>
+  </si>
+  <si>
+    <t>5.2 Display ancillary offers</t>
+  </si>
+  <si>
+    <t>5.3 Explain and control personalization</t>
+  </si>
+  <si>
+    <t>AQPI-14</t>
+  </si>
+  <si>
+    <t>[Epic 4] Cart Management</t>
+  </si>
+  <si>
+    <t>6.1 Add room selection to cart</t>
+  </si>
+  <si>
+    <t>6.2 Add, update, and remove ancillaries</t>
+  </si>
+  <si>
+    <t>6.3 Review cart and total price</t>
+  </si>
+  <si>
+    <t>AQPI-18</t>
+  </si>
+  <si>
+    <t>[Epic 5] Checkout and Reservation</t>
+  </si>
+  <si>
+    <t>7.1 Capture guest and contact information</t>
+  </si>
+  <si>
     <t>failing</t>
   </si>
   <si>
-    <t>10.3 Allow up to 5 confirmation resends</t>
-  </si>
-  <si>
-    <t>10.4 Cancel a reservation free of charge</t>
-  </si>
-  <si>
-    <t>AQPI-23</t>
-  </si>
-  <si>
-    <t>[Epic 6] Confirmation and Notifications</t>
-  </si>
-  <si>
-    <t>8.1 Generate confirmation message</t>
-  </si>
-  <si>
-    <t>8.2 Send and track confirmation email</t>
-  </si>
-  <si>
-    <t>8.3 Resend confirmation safely</t>
-  </si>
-  <si>
-    <t>8.4 Send a cancellation e-mail</t>
-  </si>
-  <si>
-    <t>initiative</t>
-  </si>
-  <si>
-    <t>baseline</t>
-  </si>
-  <si>
-    <t>[Initiative] Intelligent Hotel Shopping and Reservation Experience</t>
-  </si>
-  <si>
-    <t>AQPI-2</t>
-  </si>
-  <si>
-    <t>[Epic 1] Search and Availability</t>
-  </si>
-  <si>
-    <t>3.1 Search hotels by destination and date range</t>
-  </si>
-  <si>
-    <t>3.2 Validate occupancy and stay criteria</t>
-  </si>
-  <si>
-    <t>3.3 Handle unavailable or failed searches</t>
-  </si>
-  <si>
-    <t>AQPI-6</t>
-  </si>
-  <si>
-    <t>[Epic 2] Hotel Results and Selection</t>
-  </si>
-  <si>
-    <t>4.1 Display available hotels</t>
-  </si>
-  <si>
-    <t>4.2 Sort and filter hotel results</t>
-  </si>
-  <si>
-    <t>4.3 View hotel and room details</t>
-  </si>
-  <si>
-    <t>AQPI-10</t>
-  </si>
-  <si>
-    <t>[Epic 3] Personalized Ancillary Offers</t>
-  </si>
-  <si>
-    <t>5.1 Determine eligible ancillary offers</t>
-  </si>
-  <si>
-    <t>5.2 Display ancillary offers</t>
-  </si>
-  <si>
-    <t>5.3 Explain and control personalization</t>
-  </si>
-  <si>
-    <t>AQPI-14</t>
-  </si>
-  <si>
-    <t>[Epic 4] Cart Management</t>
-  </si>
-  <si>
-    <t>6.1 Add room selection to cart</t>
-  </si>
-  <si>
-    <t>6.2 Add, update, and remove ancillaries</t>
-  </si>
-  <si>
-    <t>6.3 Review cart and total price</t>
-  </si>
-  <si>
-    <t>AQPI-18</t>
-  </si>
-  <si>
-    <t>[Epic 5] Checkout and Reservation</t>
-  </si>
-  <si>
-    <t>7.1 Capture guest and contact information</t>
-  </si>
-  <si>
     <t>7.2 Capture and authorize payment</t>
   </si>
   <si>
@@ -5657,7 +5618,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-12T01:35:22.376Z</t>
+    <t>2026-10-12T02:09:54.907Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5669,7 +5630,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-12T01:35:22.429Z</t>
+    <t>2026-10-12T02:09:54.949Z</t>
   </si>
   <si>
     <t>23 requirements, 29 test cases, 18 scripts merged: BL-2 v1 -&gt; v2</t>
@@ -5774,6 +5735,18 @@
     <t>input-review.md</t>
   </si>
   <si>
+    <t>release-criteria</t>
+  </si>
+  <si>
+    <t>Release criteria (Go / Conditional go / No-go)</t>
+  </si>
+  <si>
+    <t>The parameters the cycle report applies to recommend Go, Conditional go or No-go. Edit this file, or upload a replacement, to change them without a code change.</t>
+  </si>
+  <si>
+    <t>release-criteria.md</t>
+  </si>
+  <si>
     <t>test-case-authoring</t>
   </si>
   <si>
@@ -5927,10 +5900,10 @@
     <t>Cycle report agent</t>
   </si>
   <si>
-    <t>cycle-report, test-case-authoring, traceability-handover</t>
-  </si>
-  <si>
-    <t>cycleReport: delivered; comparison: delivered; testCaseExport: delivered</t>
+    <t>cycle-report, release-criteria, test-case-authoring, traceability-handover</t>
+  </si>
+  <si>
+    <t>cycleReport: delivered; comparison: delivered; releaseDecision: delivered; testCaseExport: delivered</t>
   </si>
 </sst>
 </file>
@@ -6460,7 +6433,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6468,7 +6441,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6476,7 +6449,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="2">
-        <v>95.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6492,7 +6465,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6500,7 +6473,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>44.2</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6549,19 +6522,19 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1547</v>
+        <v>1534</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1548</v>
+        <v>1535</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1549</v>
+        <v>1536</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1550</v>
+        <v>1537</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1551</v>
+        <v>1538</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
@@ -6590,16 +6563,16 @@
         <v>575</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1552</v>
+        <v>1539</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1553</v>
+        <v>1540</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1554</v>
+        <v>1541</v>
       </c>
       <c r="F2" s="2">
         <v>2</v>
@@ -6620,7 +6593,7 @@
         <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1555</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6628,16 +6601,16 @@
         <v>531</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1556</v>
+        <v>1543</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1553</v>
+        <v>1540</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1557</v>
+        <v>1544</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -6658,7 +6631,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6666,16 +6639,16 @@
         <v>558</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1556</v>
+        <v>1543</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1553</v>
+        <v>1540</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1559</v>
+        <v>1546</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -6687,16 +6660,16 @@
         <v>4</v>
       </c>
       <c r="I4" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>1467</v>
+        <v>69</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1560</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6704,16 +6677,16 @@
         <v>546</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1556</v>
+        <v>1543</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1553</v>
+        <v>1540</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1561</v>
+        <v>1547</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -6734,7 +6707,7 @@
         <v>69</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6742,16 +6715,16 @@
         <v>587</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1556</v>
+        <v>1543</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1553</v>
+        <v>1540</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1562</v>
+        <v>1548</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
@@ -6772,24 +6745,24 @@
         <v>69</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1563</v>
+        <v>1549</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1552</v>
+        <v>1539</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1553</v>
+        <v>1540</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1564</v>
+        <v>1550</v>
       </c>
       <c r="F7" s="2">
         <v>4</v>
@@ -6810,7 +6783,7 @@
         <v>69</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1555</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6818,16 +6791,16 @@
         <v>399</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1556</v>
+        <v>1543</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1553</v>
+        <v>1540</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1563</v>
+        <v>1549</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1565</v>
+        <v>1551</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -6848,7 +6821,7 @@
         <v>69</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6856,16 +6829,16 @@
         <v>418</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1556</v>
+        <v>1543</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1553</v>
+        <v>1540</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1563</v>
+        <v>1549</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1566</v>
+        <v>1552</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
@@ -6877,16 +6850,16 @@
         <v>2</v>
       </c>
       <c r="I9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>1471</v>
+        <v>69</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>1560</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6894,16 +6867,16 @@
         <v>439</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1556</v>
+        <v>1543</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>1553</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>1563</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1567</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -6924,7 +6897,7 @@
         <v>69</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6932,16 +6905,16 @@
         <v>610</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1556</v>
+        <v>1543</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1553</v>
+        <v>1540</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1563</v>
+        <v>1549</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="F11" s="2">
         <v>3</v>
@@ -6962,7 +6935,7 @@
         <v>69</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6970,16 +6943,16 @@
         <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1569</v>
+        <v>1555</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1571</v>
+        <v>1557</v>
       </c>
       <c r="F12" s="2">
         <v>2</v>
@@ -7000,24 +6973,24 @@
         <v>69</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1572</v>
+        <v>1558</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1552</v>
+        <v>1539</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1573</v>
+        <v>1559</v>
       </c>
       <c r="F13" s="2">
         <v>4</v>
@@ -7038,7 +7011,7 @@
         <v>69</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1555</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7046,16 +7019,16 @@
         <v>120</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>1572</v>
+        <v>1558</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1574</v>
+        <v>1560</v>
       </c>
       <c r="F14" s="2">
         <v>7</v>
@@ -7076,7 +7049,7 @@
         <v>69</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7084,16 +7057,16 @@
         <v>150</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>1572</v>
+        <v>1558</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1575</v>
+        <v>1561</v>
       </c>
       <c r="F15" s="2">
         <v>6</v>
@@ -7114,7 +7087,7 @@
         <v>69</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7122,16 +7095,16 @@
         <v>171</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>1572</v>
+        <v>1558</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1576</v>
+        <v>1562</v>
       </c>
       <c r="F16" s="2">
         <v>3</v>
@@ -7152,24 +7125,24 @@
         <v>69</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1577</v>
+        <v>1563</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1552</v>
+        <v>1539</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1578</v>
+        <v>1564</v>
       </c>
       <c r="F17" s="2">
         <v>4</v>
@@ -7190,7 +7163,7 @@
         <v>69</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>1555</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7198,16 +7171,16 @@
         <v>183</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>1577</v>
+        <v>1563</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1579</v>
+        <v>1565</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
@@ -7228,7 +7201,7 @@
         <v>69</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7236,16 +7209,16 @@
         <v>623</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>1577</v>
+        <v>1563</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1580</v>
+        <v>1566</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
@@ -7266,7 +7239,7 @@
         <v>69</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7274,16 +7247,16 @@
         <v>204</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>1577</v>
+        <v>1563</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1581</v>
+        <v>1567</v>
       </c>
       <c r="F20" s="2">
         <v>4</v>
@@ -7304,24 +7277,24 @@
         <v>69</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1582</v>
+        <v>1568</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1552</v>
+        <v>1539</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1583</v>
+        <v>1569</v>
       </c>
       <c r="F21" s="2">
         <v>4</v>
@@ -7342,7 +7315,7 @@
         <v>69</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1555</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7350,16 +7323,16 @@
         <v>221</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>1570</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>1582</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>1584</v>
       </c>
       <c r="F22" s="2">
         <v>7</v>
@@ -7380,7 +7353,7 @@
         <v>69</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7388,16 +7361,16 @@
         <v>250</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>1582</v>
+        <v>1568</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1585</v>
+        <v>1571</v>
       </c>
       <c r="F23" s="2">
         <v>3</v>
@@ -7418,7 +7391,7 @@
         <v>69</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7426,16 +7399,16 @@
         <v>640</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>1582</v>
+        <v>1568</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1586</v>
+        <v>1572</v>
       </c>
       <c r="F24" s="2">
         <v>3</v>
@@ -7456,24 +7429,24 @@
         <v>69</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>1587</v>
+        <v>1573</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1552</v>
+        <v>1539</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1588</v>
+        <v>1574</v>
       </c>
       <c r="F25" s="2">
         <v>4</v>
@@ -7494,7 +7467,7 @@
         <v>69</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>1555</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7502,16 +7475,16 @@
         <v>265</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>1587</v>
+        <v>1573</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1589</v>
+        <v>1575</v>
       </c>
       <c r="F26" s="2">
         <v>5</v>
@@ -7532,7 +7505,7 @@
         <v>69</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7540,16 +7513,16 @@
         <v>286</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>1587</v>
+        <v>1573</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1590</v>
+        <v>1576</v>
       </c>
       <c r="F27" s="2">
         <v>4</v>
@@ -7570,7 +7543,7 @@
         <v>69</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7578,16 +7551,16 @@
         <v>303</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>1587</v>
+        <v>1573</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1591</v>
+        <v>1577</v>
       </c>
       <c r="F28" s="2">
         <v>6</v>
@@ -7599,33 +7572,33 @@
         <v>3</v>
       </c>
       <c r="I28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>1453</v>
+        <v>69</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1560</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1552</v>
+        <v>1539</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1593</v>
+        <v>1579</v>
       </c>
       <c r="F29" s="2">
         <v>4</v>
@@ -7646,7 +7619,7 @@
         <v>69</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>1555</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7654,16 +7627,16 @@
         <v>324</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1594</v>
+        <v>1580</v>
       </c>
       <c r="F30" s="2">
         <v>6</v>
@@ -7675,16 +7648,16 @@
         <v>4</v>
       </c>
       <c r="I30" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>69</v>
+        <v>1453</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>1558</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7692,16 +7665,16 @@
         <v>349</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1595</v>
+        <v>1582</v>
       </c>
       <c r="F31" s="2">
         <v>6</v>
@@ -7722,7 +7695,7 @@
         <v>69</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7730,16 +7703,16 @@
         <v>374</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1596</v>
+        <v>1583</v>
       </c>
       <c r="F32" s="2">
         <v>7</v>
@@ -7751,16 +7724,16 @@
         <v>6</v>
       </c>
       <c r="I32" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>1461</v>
+        <v>69</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1560</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7768,16 +7741,16 @@
         <v>653</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>1592</v>
+        <v>1578</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F33" s="2">
         <v>3</v>
@@ -7798,24 +7771,24 @@
         <v>69</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1598</v>
+        <v>1585</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1552</v>
+        <v>1539</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1570</v>
+        <v>1556</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F34" s="2">
         <v>4</v>
@@ -7836,7 +7809,7 @@
         <v>69</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1555</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7844,16 +7817,16 @@
         <v>452</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>1598</v>
+        <v>1585</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1600</v>
+        <v>1587</v>
       </c>
       <c r="F35" s="2">
         <v>5</v>
@@ -7874,7 +7847,7 @@
         <v>69</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7882,16 +7855,16 @@
         <v>472</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>1598</v>
+        <v>1585</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1601</v>
+        <v>1588</v>
       </c>
       <c r="F36" s="2">
         <v>5</v>
@@ -7912,7 +7885,7 @@
         <v>69</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7920,16 +7893,16 @@
         <v>497</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>1598</v>
+        <v>1585</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1602</v>
+        <v>1589</v>
       </c>
       <c r="F37" s="2">
         <v>3</v>
@@ -7950,7 +7923,7 @@
         <v>69</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1558</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7958,16 +7931,16 @@
         <v>514</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>1570</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>1598</v>
+        <v>1585</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F38" s="2">
         <v>3</v>
@@ -7988,7 +7961,7 @@
         <v>69</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1555</v>
+        <v>1542</v>
       </c>
     </row>
   </sheetData>
@@ -8023,13 +7996,13 @@
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1604</v>
+        <v>1591</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1605</v>
+        <v>1592</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>666</v>
@@ -8038,19 +8011,19 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1606</v>
+        <v>1593</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1607</v>
+        <v>1594</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1608</v>
+        <v>1595</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1433</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1609</v>
+        <v>1596</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1444</v>
@@ -8082,10 +8055,10 @@
         <v>689</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1610</v>
+        <v>1597</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1611</v>
+        <v>1598</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>1437</v>
@@ -8123,7 +8096,7 @@
         <v>701</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1612</v>
+        <v>1599</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
@@ -8162,7 +8135,7 @@
         <v>701</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1613</v>
+        <v>1600</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
@@ -8201,7 +8174,7 @@
         <v>701</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1614</v>
+        <v>1601</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
@@ -8240,7 +8213,7 @@
         <v>701</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1615</v>
+        <v>1602</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
@@ -8279,7 +8252,7 @@
         <v>701</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1616</v>
+        <v>1603</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -8318,10 +8291,10 @@
         <v>689</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1617</v>
+        <v>1604</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1618</v>
+        <v>1605</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>1437</v>
@@ -8359,10 +8332,10 @@
         <v>689</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1619</v>
+        <v>1606</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1620</v>
+        <v>1607</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>1437</v>
@@ -8400,10 +8373,10 @@
         <v>689</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1621</v>
+        <v>1608</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1622</v>
+        <v>1609</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>1437</v>
@@ -8441,10 +8414,10 @@
         <v>689</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1623</v>
+        <v>1610</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1622</v>
+        <v>1609</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>1437</v>
@@ -8482,10 +8455,10 @@
         <v>689</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1624</v>
+        <v>1611</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1622</v>
+        <v>1609</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>1437</v>
@@ -8523,10 +8496,10 @@
         <v>689</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1625</v>
+        <v>1612</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1626</v>
+        <v>1613</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>1437</v>
@@ -8564,7 +8537,7 @@
         <v>701</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1627</v>
+        <v>1614</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -8603,7 +8576,7 @@
         <v>701</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1628</v>
+        <v>1615</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
@@ -8642,7 +8615,7 @@
         <v>701</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1629</v>
+        <v>1616</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -8681,10 +8654,10 @@
         <v>689</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1630</v>
+        <v>1617</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1631</v>
+        <v>1618</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>1437</v>
@@ -8722,10 +8695,10 @@
         <v>689</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1632</v>
+        <v>1619</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1633</v>
+        <v>1620</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>1437</v>
@@ -8763,7 +8736,7 @@
         <v>701</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1634</v>
+        <v>1621</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
@@ -8802,7 +8775,7 @@
         <v>701</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1635</v>
+        <v>1622</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
@@ -8841,10 +8814,10 @@
         <v>689</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1636</v>
+        <v>1623</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1637</v>
+        <v>1624</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>1437</v>
@@ -8882,7 +8855,7 @@
         <v>701</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1638</v>
+        <v>1625</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
@@ -8921,10 +8894,10 @@
         <v>689</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1639</v>
+        <v>1626</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1640</v>
+        <v>1627</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>1437</v>
@@ -8962,10 +8935,10 @@
         <v>689</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1641</v>
+        <v>1628</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1642</v>
+        <v>1629</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>1437</v>
@@ -9003,10 +8976,10 @@
         <v>689</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1643</v>
+        <v>1630</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1644</v>
+        <v>1631</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>1437</v>
@@ -9044,10 +9017,10 @@
         <v>689</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1645</v>
+        <v>1632</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1646</v>
+        <v>1633</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>1437</v>
@@ -9085,10 +9058,10 @@
         <v>689</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1647</v>
+        <v>1634</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1648</v>
+        <v>1635</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>1437</v>
@@ -9126,10 +9099,10 @@
         <v>689</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1649</v>
+        <v>1636</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1650</v>
+        <v>1637</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>1437</v>
@@ -9167,10 +9140,10 @@
         <v>689</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1651</v>
+        <v>1638</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1652</v>
+        <v>1639</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>1437</v>
@@ -9208,7 +9181,7 @@
         <v>701</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1653</v>
+        <v>1640</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
@@ -9247,7 +9220,7 @@
         <v>701</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1654</v>
+        <v>1641</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
@@ -9286,10 +9259,10 @@
         <v>689</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1655</v>
+        <v>1642</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1656</v>
+        <v>1643</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>1437</v>
@@ -9327,7 +9300,7 @@
         <v>701</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1657</v>
+        <v>1644</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
@@ -9366,10 +9339,10 @@
         <v>689</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1658</v>
+        <v>1645</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1659</v>
+        <v>1646</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>1437</v>
@@ -9407,10 +9380,10 @@
         <v>689</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1660</v>
+        <v>1647</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1661</v>
+        <v>1648</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>1437</v>
@@ -9448,7 +9421,7 @@
         <v>701</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1662</v>
+        <v>1649</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -9487,7 +9460,7 @@
         <v>701</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1663</v>
+        <v>1650</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
@@ -9526,7 +9499,7 @@
         <v>701</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1664</v>
+        <v>1651</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -9565,7 +9538,7 @@
         <v>701</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1665</v>
+        <v>1652</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
@@ -9604,10 +9577,10 @@
         <v>689</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1666</v>
+        <v>1653</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1667</v>
+        <v>1654</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>1437</v>
@@ -9645,10 +9618,10 @@
         <v>689</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1668</v>
+        <v>1655</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>1669</v>
+        <v>1656</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>1437</v>
@@ -9686,10 +9659,10 @@
         <v>689</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1670</v>
+        <v>1657</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>1671</v>
+        <v>1658</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>1437</v>
@@ -9727,10 +9700,10 @@
         <v>689</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1672</v>
+        <v>1659</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>1673</v>
+        <v>1660</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>1437</v>
@@ -9768,7 +9741,7 @@
         <v>701</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1674</v>
+        <v>1661</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -9807,7 +9780,7 @@
         <v>701</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1675</v>
+        <v>1662</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
@@ -9846,7 +9819,7 @@
         <v>701</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1676</v>
+        <v>1663</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
@@ -9885,7 +9858,7 @@
         <v>701</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1677</v>
+        <v>1664</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
@@ -9924,7 +9897,7 @@
         <v>701</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1678</v>
+        <v>1665</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
@@ -9963,10 +9936,10 @@
         <v>689</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1679</v>
+        <v>1666</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>1680</v>
+        <v>1667</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>1437</v>
@@ -10004,10 +9977,10 @@
         <v>689</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1681</v>
+        <v>1668</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1682</v>
+        <v>1669</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1437</v>
@@ -10045,7 +10018,7 @@
         <v>701</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1683</v>
+        <v>1670</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
@@ -10084,10 +10057,10 @@
         <v>689</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1684</v>
+        <v>1671</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>1685</v>
+        <v>1672</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>1437</v>
@@ -10125,7 +10098,7 @@
         <v>701</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1686</v>
+        <v>1673</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -10164,7 +10137,7 @@
         <v>701</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1687</v>
+        <v>1674</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -10203,7 +10176,7 @@
         <v>701</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1688</v>
+        <v>1675</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -10242,7 +10215,7 @@
         <v>701</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1689</v>
+        <v>1676</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -10281,10 +10254,10 @@
         <v>689</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1690</v>
+        <v>1677</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1691</v>
+        <v>1678</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>1437</v>
@@ -10322,10 +10295,10 @@
         <v>689</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1692</v>
+        <v>1679</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1693</v>
+        <v>1680</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>1437</v>
@@ -10363,10 +10336,10 @@
         <v>689</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1694</v>
+        <v>1681</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>1695</v>
+        <v>1682</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>1437</v>
@@ -10404,7 +10377,7 @@
         <v>701</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1696</v>
+        <v>1683</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
@@ -10443,7 +10416,7 @@
         <v>701</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1697</v>
+        <v>1684</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
@@ -10482,16 +10455,16 @@
         <v>689</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1698</v>
+        <v>1685</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>1699</v>
+        <v>1686</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>69</v>
+        <v>1453</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>69</v>
@@ -10523,10 +10496,10 @@
         <v>689</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1700</v>
+        <v>1687</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>1701</v>
+        <v>1688</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>1437</v>
@@ -10564,10 +10537,10 @@
         <v>689</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1702</v>
+        <v>1689</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>1701</v>
+        <v>1688</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>1437</v>
@@ -10605,7 +10578,7 @@
         <v>701</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1703</v>
+        <v>1690</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
@@ -10644,10 +10617,10 @@
         <v>689</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1704</v>
+        <v>1691</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>1705</v>
+        <v>1692</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>1437</v>
@@ -10685,10 +10658,10 @@
         <v>689</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1706</v>
+        <v>1693</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>1705</v>
+        <v>1692</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>1437</v>
@@ -10726,10 +10699,10 @@
         <v>689</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1707</v>
+        <v>1694</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>1705</v>
+        <v>1692</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>1437</v>
@@ -10767,10 +10740,10 @@
         <v>689</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1708</v>
+        <v>1695</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>1709</v>
+        <v>1696</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>1437</v>
@@ -10808,7 +10781,7 @@
         <v>701</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1710</v>
+        <v>1697</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
@@ -10847,7 +10820,7 @@
         <v>701</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1711</v>
+        <v>1698</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
@@ -10886,10 +10859,10 @@
         <v>689</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1712</v>
+        <v>1699</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>1713</v>
+        <v>1700</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>1437</v>
@@ -10927,10 +10900,10 @@
         <v>689</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1714</v>
+        <v>1701</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>1715</v>
+        <v>1702</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>1437</v>
@@ -10968,10 +10941,10 @@
         <v>689</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1716</v>
+        <v>1703</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1717</v>
+        <v>1704</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>1437</v>
@@ -11009,7 +10982,7 @@
         <v>701</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1718</v>
+        <v>1705</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
@@ -11048,7 +11021,7 @@
         <v>701</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>1719</v>
+        <v>1706</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
@@ -11087,7 +11060,7 @@
         <v>701</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>1720</v>
+        <v>1707</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
@@ -11126,10 +11099,10 @@
         <v>689</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1721</v>
+        <v>1708</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>1722</v>
+        <v>1709</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>1437</v>
@@ -11167,10 +11140,10 @@
         <v>689</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1723</v>
+        <v>1710</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>1724</v>
+        <v>1711</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>1437</v>
@@ -11208,7 +11181,7 @@
         <v>701</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1725</v>
+        <v>1712</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
@@ -11247,10 +11220,10 @@
         <v>689</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1726</v>
+        <v>1713</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1727</v>
+        <v>1714</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1437</v>
@@ -11288,7 +11261,7 @@
         <v>701</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1728</v>
+        <v>1715</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
@@ -11327,10 +11300,10 @@
         <v>689</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>1729</v>
+        <v>1716</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>1730</v>
+        <v>1717</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>1437</v>
@@ -11368,7 +11341,7 @@
         <v>701</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>1731</v>
+        <v>1718</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -11407,7 +11380,7 @@
         <v>701</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1732</v>
+        <v>1719</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -11446,7 +11419,7 @@
         <v>701</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>1733</v>
+        <v>1720</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
@@ -11485,10 +11458,10 @@
         <v>689</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1734</v>
+        <v>1721</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>1735</v>
+        <v>1722</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>1437</v>
@@ -11526,7 +11499,7 @@
         <v>701</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>1736</v>
+        <v>1723</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
@@ -11565,7 +11538,7 @@
         <v>701</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>1737</v>
+        <v>1724</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
@@ -11604,7 +11577,7 @@
         <v>701</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1738</v>
+        <v>1725</v>
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
@@ -11643,7 +11616,7 @@
         <v>701</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1739</v>
+        <v>1726</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
@@ -11682,7 +11655,7 @@
         <v>701</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>1740</v>
+        <v>1727</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
@@ -11721,10 +11694,10 @@
         <v>689</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1741</v>
+        <v>1728</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>1742</v>
+        <v>1729</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>1437</v>
@@ -11762,7 +11735,7 @@
         <v>701</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>1743</v>
+        <v>1730</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
@@ -11801,10 +11774,10 @@
         <v>689</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1744</v>
+        <v>1731</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>1745</v>
+        <v>1732</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>1437</v>
@@ -11842,7 +11815,7 @@
         <v>701</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>1746</v>
+        <v>1733</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
@@ -11881,7 +11854,7 @@
         <v>701</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1747</v>
+        <v>1734</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -11920,7 +11893,7 @@
         <v>701</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>1748</v>
+        <v>1735</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
@@ -11959,7 +11932,7 @@
         <v>701</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1749</v>
+        <v>1736</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -11998,7 +11971,7 @@
         <v>701</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>1750</v>
+        <v>1737</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
@@ -12037,7 +12010,7 @@
         <v>701</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1751</v>
+        <v>1738</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -12076,10 +12049,10 @@
         <v>689</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>1752</v>
+        <v>1739</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>1753</v>
+        <v>1740</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>1437</v>
@@ -12117,7 +12090,7 @@
         <v>701</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1754</v>
+        <v>1741</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
@@ -12156,7 +12129,7 @@
         <v>701</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>1755</v>
+        <v>1742</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2" t="s">
@@ -12195,7 +12168,7 @@
         <v>701</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>1756</v>
+        <v>1743</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -12234,10 +12207,10 @@
         <v>689</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1757</v>
+        <v>1744</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1758</v>
+        <v>1745</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>1437</v>
@@ -12275,10 +12248,10 @@
         <v>689</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1759</v>
+        <v>1746</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>1760</v>
+        <v>1747</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>1437</v>
@@ -12316,16 +12289,16 @@
         <v>689</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1761</v>
+        <v>1748</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1760</v>
+        <v>1747</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>1453</v>
+        <v>69</v>
       </c>
       <c r="M108" s="2" t="s">
         <v>69</v>
@@ -12357,10 +12330,10 @@
         <v>689</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1762</v>
+        <v>1749</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>1763</v>
+        <v>1750</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>1437</v>
@@ -12398,10 +12371,10 @@
         <v>689</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1764</v>
+        <v>1751</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>1765</v>
+        <v>1752</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>1437</v>
@@ -12439,16 +12412,16 @@
         <v>689</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1766</v>
+        <v>1753</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>1765</v>
+        <v>1752</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>1461</v>
+        <v>69</v>
       </c>
       <c r="M111" s="2" t="s">
         <v>69</v>
@@ -12480,10 +12453,10 @@
         <v>689</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1767</v>
+        <v>1754</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>1765</v>
+        <v>1752</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>1437</v>
@@ -12521,10 +12494,10 @@
         <v>689</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1768</v>
+        <v>1755</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>1769</v>
+        <v>1756</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>1437</v>
@@ -12562,10 +12535,10 @@
         <v>689</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1770</v>
+        <v>1757</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>1769</v>
+        <v>1756</v>
       </c>
       <c r="K114" s="2" t="s">
         <v>1437</v>
@@ -12603,10 +12576,10 @@
         <v>689</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1771</v>
+        <v>1758</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>1769</v>
+        <v>1756</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>1437</v>
@@ -12644,16 +12617,16 @@
         <v>689</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1772</v>
+        <v>1759</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>1769</v>
+        <v>1756</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>1467</v>
+        <v>69</v>
       </c>
       <c r="M116" s="2" t="s">
         <v>69</v>
@@ -12685,10 +12658,10 @@
         <v>689</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1773</v>
+        <v>1760</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1774</v>
+        <v>1761</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1437</v>
@@ -12726,10 +12699,10 @@
         <v>689</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1775</v>
+        <v>1762</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>1774</v>
+        <v>1761</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>1437</v>
@@ -12767,10 +12740,10 @@
         <v>689</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1776</v>
+        <v>1763</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>1774</v>
+        <v>1761</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>1437</v>
@@ -12808,10 +12781,10 @@
         <v>689</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1777</v>
+        <v>1764</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1774</v>
+        <v>1761</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>1437</v>
@@ -12849,10 +12822,10 @@
         <v>689</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1778</v>
+        <v>1765</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1779</v>
+        <v>1766</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>1437</v>
@@ -12890,10 +12863,10 @@
         <v>689</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1780</v>
+        <v>1767</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1779</v>
+        <v>1766</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>1437</v>
@@ -12931,7 +12904,7 @@
         <v>701</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1781</v>
+        <v>1768</v>
       </c>
       <c r="J123" s="2"/>
       <c r="K123" s="2" t="s">
@@ -12970,7 +12943,7 @@
         <v>701</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1782</v>
+        <v>1769</v>
       </c>
       <c r="J124" s="2"/>
       <c r="K124" s="2" t="s">
@@ -13009,10 +12982,10 @@
         <v>689</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1783</v>
+        <v>1770</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1784</v>
+        <v>1771</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>1437</v>
@@ -13050,10 +13023,10 @@
         <v>689</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>1785</v>
+        <v>1772</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>1784</v>
+        <v>1771</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>1437</v>
@@ -13091,10 +13064,10 @@
         <v>689</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>1786</v>
+        <v>1773</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>1787</v>
+        <v>1774</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>1437</v>
@@ -13132,10 +13105,10 @@
         <v>689</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>1788</v>
+        <v>1775</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>1789</v>
+        <v>1776</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>1437</v>
@@ -13173,10 +13146,10 @@
         <v>689</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>1790</v>
+        <v>1777</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1791</v>
+        <v>1778</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>1437</v>
@@ -13214,10 +13187,10 @@
         <v>689</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>1792</v>
+        <v>1779</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>1791</v>
+        <v>1778</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>1437</v>
@@ -13255,16 +13228,16 @@
         <v>689</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>1793</v>
+        <v>1780</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1794</v>
+        <v>1781</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>1471</v>
+        <v>69</v>
       </c>
       <c r="M131" s="2" t="s">
         <v>69</v>
@@ -13296,10 +13269,10 @@
         <v>689</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1795</v>
+        <v>1782</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1796</v>
+        <v>1783</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1437</v>
@@ -13337,10 +13310,10 @@
         <v>689</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1797</v>
+        <v>1784</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1798</v>
+        <v>1785</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>1437</v>
@@ -13378,7 +13351,7 @@
         <v>701</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>1799</v>
+        <v>1786</v>
       </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2" t="s">
@@ -13417,10 +13390,10 @@
         <v>689</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>1800</v>
+        <v>1787</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>1801</v>
+        <v>1788</v>
       </c>
       <c r="K135" s="2" t="s">
         <v>1437</v>
@@ -13458,10 +13431,10 @@
         <v>689</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>1802</v>
+        <v>1789</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1803</v>
+        <v>1790</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>1437</v>
@@ -13499,10 +13472,10 @@
         <v>689</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>1804</v>
+        <v>1791</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>1803</v>
+        <v>1790</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>1437</v>
@@ -13540,7 +13513,7 @@
         <v>701</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>1805</v>
+        <v>1792</v>
       </c>
       <c r="J138" s="2"/>
       <c r="K138" s="2" t="s">
@@ -13579,10 +13552,10 @@
         <v>689</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>1806</v>
+        <v>1793</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>1807</v>
+        <v>1794</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>1437</v>
@@ -13620,7 +13593,7 @@
         <v>701</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>1808</v>
+        <v>1795</v>
       </c>
       <c r="J140" s="2"/>
       <c r="K140" s="2" t="s">
@@ -13659,10 +13632,10 @@
         <v>689</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>1809</v>
+        <v>1796</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>1810</v>
+        <v>1797</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>1437</v>
@@ -13700,10 +13673,10 @@
         <v>689</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>1811</v>
+        <v>1798</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>1812</v>
+        <v>1799</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>1437</v>
@@ -13741,10 +13714,10 @@
         <v>689</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>1813</v>
+        <v>1800</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>1814</v>
+        <v>1801</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>1437</v>
@@ -13782,10 +13755,10 @@
         <v>689</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>1815</v>
+        <v>1802</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>1816</v>
+        <v>1803</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>1437</v>
@@ -13823,10 +13796,10 @@
         <v>689</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>1817</v>
+        <v>1804</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>1818</v>
+        <v>1805</v>
       </c>
       <c r="K145" s="2" t="s">
         <v>1437</v>
@@ -13862,40 +13835,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1819</v>
+        <v>1806</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1820</v>
+        <v>1807</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1821</v>
+        <v>1808</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1822</v>
+        <v>1809</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1823</v>
+        <v>1810</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1824</v>
+        <v>1811</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1825</v>
+        <v>1812</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1826</v>
+        <v>1813</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1827</v>
+        <v>1814</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1828</v>
+        <v>1815</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1435</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1829</v>
+        <v>1816</v>
       </c>
     </row>
   </sheetData>
@@ -13918,53 +13891,53 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1830</v>
+        <v>1817</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1831</v>
+        <v>1818</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1832</v>
+        <v>1819</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1823</v>
+        <v>1810</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1833</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1834</v>
+        <v>1821</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1835</v>
+        <v>1822</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1836</v>
+        <v>1823</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1837</v>
+        <v>1824</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1838</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1839</v>
+        <v>1826</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1835</v>
+        <v>1822</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1840</v>
+        <v>1827</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1841</v>
+        <v>1828</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1842</v>
+        <v>1829</v>
       </c>
     </row>
   </sheetData>
@@ -13975,7 +13948,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -13987,189 +13960,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1843</v>
+        <v>1830</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1502</v>
+        <v>1490</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1844</v>
+        <v>1831</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1845</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1846</v>
+        <v>1833</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1847</v>
+        <v>1834</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1848</v>
+        <v>1835</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1849</v>
+        <v>1836</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1850</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1851</v>
+        <v>1838</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1852</v>
+        <v>1839</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1853</v>
+        <v>1840</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1854</v>
+        <v>1841</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1855</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1856</v>
+        <v>1843</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1857</v>
+        <v>1844</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1858</v>
+        <v>1845</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1859</v>
+        <v>1846</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1860</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1861</v>
+        <v>1848</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1862</v>
+        <v>1849</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1863</v>
+        <v>1850</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1864</v>
+        <v>1851</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1865</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1866</v>
+        <v>1853</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1867</v>
+        <v>1854</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1868</v>
+        <v>1855</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1869</v>
+        <v>1856</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1870</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1871</v>
+        <v>1858</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1872</v>
+        <v>1859</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1873</v>
+        <v>1860</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1874</v>
+        <v>1861</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1875</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1876</v>
+        <v>1863</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1877</v>
+        <v>1864</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1878</v>
+        <v>1865</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1879</v>
+        <v>1841</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1880</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1881</v>
+        <v>1867</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1882</v>
+        <v>1868</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1883</v>
+        <v>1869</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1884</v>
+        <v>1870</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1885</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1886</v>
+        <v>1872</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1887</v>
+        <v>1873</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1888</v>
+        <v>1874</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1889</v>
+        <v>1875</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1890</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1891</v>
+        <v>1877</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1892</v>
+        <v>1878</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1893</v>
+        <v>1879</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1894</v>
+        <v>1880</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1895</v>
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1886</v>
       </c>
     </row>
   </sheetData>
@@ -14192,186 +14182,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1896</v>
+        <v>1887</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1897</v>
+        <v>1888</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1898</v>
+        <v>1889</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1899</v>
+        <v>1890</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1900</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1901</v>
+        <v>1892</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1902</v>
+        <v>1893</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1904</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1871</v>
+        <v>1858</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1905</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1906</v>
+        <v>1897</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1861</v>
+        <v>1848</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1907</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1908</v>
+        <v>1899</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1909</v>
+        <v>1900</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1910</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1911</v>
+        <v>1902</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1912</v>
+        <v>1903</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1913</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1914</v>
+        <v>1905</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1915</v>
+        <v>1906</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1916</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1917</v>
+        <v>1908</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1918</v>
+        <v>1909</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1919</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1920</v>
+        <v>1911</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1921</v>
+        <v>1912</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1922</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1923</v>
+        <v>1914</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1924</v>
+        <v>1915</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1925</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1926</v>
+        <v>1917</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1927</v>
+        <v>1918</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1928</v>
+        <v>1919</v>
       </c>
     </row>
   </sheetData>
@@ -26806,7 +26796,7 @@
         <v>1437</v>
       </c>
       <c r="E2" s="2">
-        <v>579</v>
+        <v>525</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -26930,7 +26920,7 @@
         <v>1437</v>
       </c>
       <c r="E8" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -26949,7 +26939,7 @@
         <v>1437</v>
       </c>
       <c r="E9" s="2">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -26968,7 +26958,7 @@
         <v>1437</v>
       </c>
       <c r="E10" s="2">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -26987,7 +26977,7 @@
         <v>1437</v>
       </c>
       <c r="E11" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -27025,7 +27015,7 @@
         <v>1437</v>
       </c>
       <c r="E13" s="2">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -27107,7 +27097,7 @@
         <v>1437</v>
       </c>
       <c r="E17" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -27126,7 +27116,7 @@
         <v>1437</v>
       </c>
       <c r="E18" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -27187,7 +27177,7 @@
         <v>1437</v>
       </c>
       <c r="E21" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -27227,7 +27217,7 @@
         <v>1437</v>
       </c>
       <c r="E23" s="2">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -27246,7 +27236,7 @@
         <v>1437</v>
       </c>
       <c r="E24" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -27265,7 +27255,7 @@
         <v>1437</v>
       </c>
       <c r="E25" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -27284,7 +27274,7 @@
         <v>1437</v>
       </c>
       <c r="E26" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -27303,7 +27293,7 @@
         <v>1437</v>
       </c>
       <c r="E27" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -27322,7 +27312,7 @@
         <v>1437</v>
       </c>
       <c r="E28" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -27341,7 +27331,7 @@
         <v>1437</v>
       </c>
       <c r="E29" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -27402,7 +27392,7 @@
         <v>1437</v>
       </c>
       <c r="E32" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -27442,7 +27432,7 @@
         <v>1437</v>
       </c>
       <c r="E34" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -27461,7 +27451,7 @@
         <v>1437</v>
       </c>
       <c r="E35" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -27564,7 +27554,7 @@
         <v>1437</v>
       </c>
       <c r="E40" s="2">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -27583,7 +27573,7 @@
         <v>1437</v>
       </c>
       <c r="E41" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -27602,7 +27592,7 @@
         <v>1437</v>
       </c>
       <c r="E42" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -27621,7 +27611,7 @@
         <v>1437</v>
       </c>
       <c r="E43" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -27745,7 +27735,7 @@
         <v>1437</v>
       </c>
       <c r="E49" s="2">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -27764,7 +27754,7 @@
         <v>1437</v>
       </c>
       <c r="E50" s="2">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -27804,7 +27794,7 @@
         <v>1437</v>
       </c>
       <c r="E52" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -27907,7 +27897,7 @@
         <v>1437</v>
       </c>
       <c r="E57" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -27926,7 +27916,7 @@
         <v>1437</v>
       </c>
       <c r="E58" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -27945,7 +27935,7 @@
         <v>1437</v>
       </c>
       <c r="E59" s="2">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -28003,10 +27993,10 @@
         <v>996</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="E62" s="2">
-        <v>245</v>
+        <v>30029</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -28025,7 +28015,7 @@
         <v>1437</v>
       </c>
       <c r="E63" s="2">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -28044,7 +28034,7 @@
         <v>1437</v>
       </c>
       <c r="E64" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -28084,7 +28074,7 @@
         <v>1437</v>
       </c>
       <c r="E66" s="2">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -28103,7 +28093,7 @@
         <v>1437</v>
       </c>
       <c r="E67" s="2">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -28122,7 +28112,7 @@
         <v>1437</v>
       </c>
       <c r="E68" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -28141,7 +28131,7 @@
         <v>1437</v>
       </c>
       <c r="E69" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -28202,7 +28192,7 @@
         <v>1437</v>
       </c>
       <c r="E72" s="2">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -28221,7 +28211,7 @@
         <v>1437</v>
       </c>
       <c r="E73" s="2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -28240,7 +28230,7 @@
         <v>1437</v>
       </c>
       <c r="E74" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -28322,7 +28312,7 @@
         <v>1437</v>
       </c>
       <c r="E78" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -28341,7 +28331,7 @@
         <v>1437</v>
       </c>
       <c r="E79" s="2">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -28381,7 +28371,7 @@
         <v>1437</v>
       </c>
       <c r="E81" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -28421,7 +28411,7 @@
         <v>1437</v>
       </c>
       <c r="E83" s="2">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -28503,7 +28493,7 @@
         <v>1437</v>
       </c>
       <c r="E87" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -28627,7 +28617,7 @@
         <v>1437</v>
       </c>
       <c r="E93" s="2">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -28667,7 +28657,7 @@
         <v>1437</v>
       </c>
       <c r="E95" s="2">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -28812,7 +28802,7 @@
         <v>1437</v>
       </c>
       <c r="E102" s="2">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -28894,7 +28884,7 @@
         <v>1437</v>
       </c>
       <c r="E106" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -28913,7 +28903,7 @@
         <v>1437</v>
       </c>
       <c r="E107" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -28929,10 +28919,10 @@
         <v>1215</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E108" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -28951,7 +28941,7 @@
         <v>1437</v>
       </c>
       <c r="E109" s="2">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -28970,7 +28960,7 @@
         <v>1437</v>
       </c>
       <c r="E110" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -28986,10 +28976,10 @@
         <v>1234</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E111" s="2">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -29008,7 +28998,7 @@
         <v>1437</v>
       </c>
       <c r="E112" s="2">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -29027,7 +29017,7 @@
         <v>1437</v>
       </c>
       <c r="E113" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -29046,7 +29036,7 @@
         <v>1437</v>
       </c>
       <c r="E114" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -29065,7 +29055,7 @@
         <v>1437</v>
       </c>
       <c r="E115" s="2">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -29081,10 +29071,10 @@
         <v>1263</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E116" s="2">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -29103,7 +29093,7 @@
         <v>1437</v>
       </c>
       <c r="E117" s="2">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -29122,7 +29112,7 @@
         <v>1437</v>
       </c>
       <c r="E118" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -29141,7 +29131,7 @@
         <v>1437</v>
       </c>
       <c r="E119" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -29160,7 +29150,7 @@
         <v>1437</v>
       </c>
       <c r="E120" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -29179,7 +29169,7 @@
         <v>1437</v>
       </c>
       <c r="E121" s="2">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -29198,7 +29188,7 @@
         <v>1437</v>
       </c>
       <c r="E122" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -29259,7 +29249,7 @@
         <v>1437</v>
       </c>
       <c r="E125" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -29278,7 +29268,7 @@
         <v>1437</v>
       </c>
       <c r="E126" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -29297,7 +29287,7 @@
         <v>1437</v>
       </c>
       <c r="E127" s="2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -29316,7 +29306,7 @@
         <v>1437</v>
       </c>
       <c r="E128" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -29335,7 +29325,7 @@
         <v>1437</v>
       </c>
       <c r="E129" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
@@ -29354,7 +29344,7 @@
         <v>1437</v>
       </c>
       <c r="E130" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -29370,10 +29360,10 @@
         <v>1350</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E131" s="2">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
@@ -29392,7 +29382,7 @@
         <v>1437</v>
       </c>
       <c r="E132" s="2">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -29411,7 +29401,7 @@
         <v>1437</v>
       </c>
       <c r="E133" s="2">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
@@ -29451,7 +29441,7 @@
         <v>1437</v>
       </c>
       <c r="E135" s="2">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -29470,7 +29460,7 @@
         <v>1437</v>
       </c>
       <c r="E136" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
@@ -29489,7 +29479,7 @@
         <v>1437</v>
       </c>
       <c r="E137" s="2">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
@@ -29529,7 +29519,7 @@
         <v>1437</v>
       </c>
       <c r="E139" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
@@ -29569,7 +29559,7 @@
         <v>1437</v>
       </c>
       <c r="E141" s="2">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -29588,7 +29578,7 @@
         <v>1437</v>
       </c>
       <c r="E142" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -29607,7 +29597,7 @@
         <v>1437</v>
       </c>
       <c r="E143" s="2">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -29626,7 +29616,7 @@
         <v>1437</v>
       </c>
       <c r="E144" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -29645,7 +29635,7 @@
         <v>1437</v>
       </c>
       <c r="E145" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
@@ -29658,7 +29648,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -29729,153 +29719,36 @@
         <v>1454</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>1455</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>1456</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>1457</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>1458</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>1459</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>1460</v>
+        <v>580</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-    </row>
-    <row r="3" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1461</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1462</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1463</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>1464</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>1465</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>1466</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>1460</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>1467</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1468</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1469</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1464</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>1466</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>1471</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1472</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1473</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1349</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1474</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>1475</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29885,7 +29758,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -29909,10 +29782,10 @@
         <v>1432</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1476</v>
+        <v>1458</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1477</v>
+        <v>1459</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1433</v>
@@ -29921,117 +29794,175 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1478</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1479</v>
+        <v>1461</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1480</v>
+        <v>1462</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>623</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>1481</v>
+        <v>1463</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1482</v>
+        <v>1464</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1483</v>
+        <v>1465</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1484</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1485</v>
+        <v>1467</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1486</v>
+        <v>1468</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>640</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>1481</v>
+        <v>1463</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1482</v>
+        <v>1464</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1483</v>
+        <v>1465</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1487</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1488</v>
+        <v>1470</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1489</v>
+        <v>1471</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>653</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>1481</v>
+        <v>1463</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1482</v>
+        <v>1464</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1483</v>
+        <v>1465</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1490</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1491</v>
+        <v>1473</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1492</v>
+        <v>1474</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>150</v>
+        <v>303</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1286</v>
+        <v>1214</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1481</v>
+        <v>1463</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1482</v>
+        <v>1464</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1483</v>
+        <v>1465</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1493</v>
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>1481</v>
       </c>
     </row>
   </sheetData>
@@ -30058,16 +29989,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1494</v>
+        <v>1482</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1495</v>
+        <v>1483</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>689</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1496</v>
+        <v>1484</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -30096,7 +30027,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30119,7 +30050,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30142,7 +30073,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30165,7 +30096,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30188,7 +30119,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30211,7 +30142,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30234,7 +30165,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30257,7 +30188,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30280,7 +30211,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30303,7 +30234,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30326,7 +30257,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30349,7 +30280,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30372,7 +30303,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30395,7 +30326,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30418,7 +30349,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30441,7 +30372,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30464,7 +30395,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30487,7 +30418,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30510,7 +30441,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30533,7 +30464,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30556,7 +30487,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30579,7 +30510,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30602,7 +30533,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30625,7 +30556,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30648,7 +30579,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30671,7 +30602,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30694,7 +30625,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30717,7 +30648,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30740,7 +30671,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30763,7 +30694,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30786,7 +30717,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30809,7 +30740,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30832,7 +30763,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30855,7 +30786,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30878,7 +30809,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30901,7 +30832,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30924,7 +30855,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30947,7 +30878,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30970,7 +30901,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30993,7 +30924,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31016,7 +30947,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31039,7 +30970,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31062,7 +30993,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31085,7 +31016,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31108,7 +31039,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31131,7 +31062,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31154,7 +31085,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31177,7 +31108,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31200,7 +31131,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31223,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31246,7 +31177,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31269,7 +31200,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31292,7 +31223,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31315,7 +31246,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31338,7 +31269,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31361,7 +31292,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31384,7 +31315,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31407,7 +31338,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31430,7 +31361,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31453,7 +31384,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31476,7 +31407,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31499,7 +31430,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31522,7 +31453,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31545,7 +31476,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31568,7 +31499,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31591,7 +31522,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31611,10 +31542,10 @@
         <v>1</v>
       </c>
       <c r="F68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1498</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31637,7 +31568,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31660,7 +31591,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31683,7 +31614,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31706,7 +31637,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31729,7 +31660,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31752,7 +31683,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31775,7 +31706,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31798,7 +31729,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31821,7 +31752,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31844,7 +31775,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31867,7 +31798,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31890,7 +31821,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31913,7 +31844,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31936,7 +31867,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31959,7 +31890,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31982,7 +31913,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32005,7 +31936,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32028,7 +31959,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32051,7 +31982,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32074,7 +32005,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32097,7 +32028,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32120,7 +32051,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32143,7 +32074,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32166,7 +32097,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32189,7 +32120,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32212,7 +32143,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32235,7 +32166,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32258,7 +32189,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32281,7 +32212,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32304,7 +32235,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32327,7 +32258,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32350,7 +32281,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32373,7 +32304,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32396,7 +32327,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32419,7 +32350,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32442,7 +32373,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32465,7 +32396,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32488,7 +32419,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32511,7 +32442,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32534,7 +32465,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32557,7 +32488,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1497</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32580,7 +32511,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32603,7 +32534,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32626,7 +32557,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32649,7 +32580,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32669,10 +32600,10 @@
         <v>2</v>
       </c>
       <c r="F114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1500</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32695,7 +32626,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32715,10 +32646,10 @@
         <v>3</v>
       </c>
       <c r="F116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1500</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32738,10 +32669,10 @@
         <v>4</v>
       </c>
       <c r="F117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1500</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32764,7 +32695,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32787,7 +32718,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32810,7 +32741,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32833,7 +32764,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32856,7 +32787,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32879,7 +32810,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32902,7 +32833,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32925,7 +32856,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32945,10 +32876,10 @@
         <v>1</v>
       </c>
       <c r="F126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>1500</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32971,7 +32902,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32994,7 +32925,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33017,7 +32948,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="130" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33040,7 +32971,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="131" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33063,7 +32994,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="132" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33086,7 +33017,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="133" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33109,7 +33040,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="134" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33132,7 +33063,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="135" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33155,7 +33086,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="136" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33178,7 +33109,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="137" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33201,7 +33132,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="138" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33224,7 +33155,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="139" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33247,7 +33178,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
   </sheetData>
@@ -33269,13 +33200,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1501</v>
+        <v>1489</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1502</v>
+        <v>1490</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1503</v>
+        <v>1491</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -33283,212 +33214,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1504</v>
+        <v>1492</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1505</v>
+        <v>1493</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1506</v>
+        <v>1494</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1507</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1508</v>
+        <v>1496</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1509</v>
+        <v>1497</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1510</v>
+        <v>1498</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1512</v>
+        <v>1499</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1513</v>
+        <v>1500</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1514</v>
+        <v>1501</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1507</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1515</v>
+        <v>1502</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1516</v>
+        <v>1503</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1517</v>
+        <v>1504</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1518</v>
+        <v>1505</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1519</v>
+        <v>1506</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1520</v>
+        <v>1507</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1521</v>
+        <v>1508</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1522</v>
+        <v>1509</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1280</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1523</v>
+        <v>1510</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1524</v>
+        <v>1511</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1525</v>
+        <v>1512</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1526</v>
+        <v>1513</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1527</v>
+        <v>1514</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1528</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1529</v>
+        <v>1516</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1530</v>
+        <v>1517</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1531</v>
+        <v>1518</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1507</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1532</v>
+        <v>1519</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1533</v>
+        <v>1520</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1534</v>
+        <v>1521</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1535</v>
+        <v>1522</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1536</v>
+        <v>1523</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1537</v>
+        <v>1524</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1538</v>
+        <v>1525</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1539</v>
+        <v>1526</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1507</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1540</v>
+        <v>1527</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1541</v>
+        <v>1528</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1542</v>
+        <v>1529</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1543</v>
+        <v>1530</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1544</v>
+        <v>1531</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>980</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1511</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1545</v>
+        <v>1532</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1546</v>
+        <v>1533</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1528</v>
+        <v>1515</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-hotel-release-2-functional-CYC-3/08-report/CYC-3-cycle-report.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7072" uniqueCount="1920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7061" uniqueCount="1912">
   <si>
     <t>Metric</t>
   </si>
@@ -169,7 +169,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 20 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 82 passed and 1 failed (pass rate 98.8%). 1 defect(s) were raised from real failures: DEF-010 Support staff see a masked e-mail and other callers are refused: failed.</t>
+    <t>Hotel booking release 2.0 (AQPI-32 + AQPI-23) (incremental) worked from Jira epic AQPI-32, AQPI-23 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) (pulled live from GitHub). The reviewed requirement set holds 138 requirements (20 unchanged · 3 enhanced · 20 new). 144 test cases are designed, 83 of them automated in 65 Playwright scripts. Execution ran 83 automated cases for real: 83 passed and 0 failed (pass rate 100%). No defects were raised.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -220,7 +220,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) at 2026-10-12T02:09:53.132Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform-v2 (e0dab1c) at 2026-10-12T02:22:18.384Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4466,9 +4466,6 @@
     <t>Manual test case - not automated, not executed</t>
   </si>
   <si>
-    <t>failed</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -4505,21 +4502,6 @@
     <t>AI likely cause</t>
   </si>
   <si>
-    <t>DEF-010</t>
-  </si>
-  <si>
-    <t>Support staff see a masked e-mail and other callers are refused: failed</t>
-  </si>
-  <si>
-    <t>not raised in Jira; linked to AQPI-19 in the platform</t>
-  </si>
-  <si>
-    <t>(see failing assertion)</t>
-  </si>
-  <si>
-    <t>Test timeout of 30000ms exceeded.</t>
-  </si>
-  <si>
     <t>First seen</t>
   </si>
   <si>
@@ -4610,9 +4592,6 @@
     <t>designed only (manual)</t>
   </si>
   <si>
-    <t>executed - failing</t>
-  </si>
-  <si>
     <t>Attribute</t>
   </si>
   <si>
@@ -4889,9 +4868,6 @@
     <t>7.1 Capture guest and contact information</t>
   </si>
   <si>
-    <t>failing</t>
-  </si>
-  <si>
     <t>7.2 Capture and authorize payment</t>
   </si>
   <si>
@@ -5618,7 +5594,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-12T02:09:54.907Z</t>
+    <t>2026-10-12T02:22:19.804Z</t>
   </si>
   <si>
     <t>43 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5630,7 +5606,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-10-12T02:09:54.949Z</t>
+    <t>2026-10-12T02:22:19.850Z</t>
   </si>
   <si>
     <t>23 requirements, 29 test cases, 18 scripts merged: BL-2 v1 -&gt; v2</t>
@@ -6433,7 +6409,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6441,7 +6417,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6449,7 +6425,7 @@
         <v>24</v>
       </c>
       <c r="B16" s="2">
-        <v>98.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6465,7 +6441,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6473,7 +6449,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>46.4</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6522,19 +6498,19 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1534</v>
+        <v>1527</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1535</v>
+        <v>1528</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1536</v>
+        <v>1529</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1537</v>
+        <v>1530</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1538</v>
+        <v>1531</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
@@ -6563,16 +6539,16 @@
         <v>575</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1541</v>
+        <v>1534</v>
       </c>
       <c r="F2" s="2">
         <v>2</v>
@@ -6593,7 +6569,7 @@
         <v>69</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6601,16 +6577,16 @@
         <v>531</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -6631,7 +6607,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6639,16 +6615,16 @@
         <v>558</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1546</v>
+        <v>1539</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -6669,7 +6645,7 @@
         <v>69</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6677,16 +6653,16 @@
         <v>546</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1547</v>
+        <v>1540</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -6707,7 +6683,7 @@
         <v>69</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6715,16 +6691,16 @@
         <v>587</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>575</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1548</v>
+        <v>1541</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
@@ -6745,24 +6721,24 @@
         <v>69</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1549</v>
+        <v>1542</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1550</v>
+        <v>1543</v>
       </c>
       <c r="F7" s="2">
         <v>4</v>
@@ -6783,7 +6759,7 @@
         <v>69</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6791,16 +6767,16 @@
         <v>399</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1549</v>
+        <v>1542</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1551</v>
+        <v>1544</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -6821,7 +6797,7 @@
         <v>69</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6829,16 +6805,16 @@
         <v>418</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1549</v>
+        <v>1542</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1552</v>
+        <v>1545</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
@@ -6859,7 +6835,7 @@
         <v>69</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6867,16 +6843,16 @@
         <v>439</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1549</v>
+        <v>1542</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1553</v>
+        <v>1546</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -6897,7 +6873,7 @@
         <v>69</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6905,16 +6881,16 @@
         <v>610</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1549</v>
+        <v>1542</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1554</v>
+        <v>1547</v>
       </c>
       <c r="F11" s="2">
         <v>3</v>
@@ -6935,7 +6911,7 @@
         <v>69</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6943,16 +6919,16 @@
         <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1557</v>
+        <v>1550</v>
       </c>
       <c r="F12" s="2">
         <v>2</v>
@@ -6973,24 +6949,24 @@
         <v>69</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1559</v>
+        <v>1552</v>
       </c>
       <c r="F13" s="2">
         <v>4</v>
@@ -7011,7 +6987,7 @@
         <v>69</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7019,16 +6995,16 @@
         <v>120</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="F14" s="2">
         <v>7</v>
@@ -7049,7 +7025,7 @@
         <v>69</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7057,16 +7033,16 @@
         <v>150</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
       <c r="F15" s="2">
         <v>6</v>
@@ -7087,7 +7063,7 @@
         <v>69</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7095,16 +7071,16 @@
         <v>171</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
       <c r="F16" s="2">
         <v>3</v>
@@ -7125,24 +7101,24 @@
         <v>69</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="F17" s="2">
         <v>4</v>
@@ -7163,7 +7139,7 @@
         <v>69</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7171,16 +7147,16 @@
         <v>183</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>1563</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
@@ -7201,7 +7177,7 @@
         <v>69</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7209,16 +7185,16 @@
         <v>623</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>1563</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
@@ -7239,7 +7215,7 @@
         <v>69</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7247,16 +7223,16 @@
         <v>204</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>1563</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
       <c r="F20" s="2">
         <v>4</v>
@@ -7277,24 +7253,24 @@
         <v>69</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1569</v>
+        <v>1562</v>
       </c>
       <c r="F21" s="2">
         <v>4</v>
@@ -7315,7 +7291,7 @@
         <v>69</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7323,16 +7299,16 @@
         <v>221</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
       <c r="F22" s="2">
         <v>7</v>
@@ -7353,7 +7329,7 @@
         <v>69</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7361,16 +7337,16 @@
         <v>250</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
       <c r="F23" s="2">
         <v>3</v>
@@ -7391,7 +7367,7 @@
         <v>69</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7399,16 +7375,16 @@
         <v>640</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
       <c r="F24" s="2">
         <v>3</v>
@@ -7429,24 +7405,24 @@
         <v>69</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
       <c r="F25" s="2">
         <v>4</v>
@@ -7467,7 +7443,7 @@
         <v>69</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7475,16 +7451,16 @@
         <v>265</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
       <c r="F26" s="2">
         <v>5</v>
@@ -7505,7 +7481,7 @@
         <v>69</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7513,16 +7489,16 @@
         <v>286</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
       <c r="F27" s="2">
         <v>4</v>
@@ -7543,7 +7519,7 @@
         <v>69</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7551,16 +7527,16 @@
         <v>303</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
       <c r="F28" s="2">
         <v>6</v>
@@ -7581,24 +7557,24 @@
         <v>69</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F29" s="2">
         <v>4</v>
@@ -7619,7 +7595,7 @@
         <v>69</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7627,16 +7603,16 @@
         <v>324</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1580</v>
+        <v>1573</v>
       </c>
       <c r="F30" s="2">
         <v>6</v>
@@ -7648,16 +7624,16 @@
         <v>4</v>
       </c>
       <c r="I30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>1453</v>
+        <v>69</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>1581</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7665,16 +7641,16 @@
         <v>349</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1582</v>
+        <v>1574</v>
       </c>
       <c r="F31" s="2">
         <v>6</v>
@@ -7695,7 +7671,7 @@
         <v>69</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7703,16 +7679,16 @@
         <v>374</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="F32" s="2">
         <v>7</v>
@@ -7733,7 +7709,7 @@
         <v>69</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7741,16 +7717,16 @@
         <v>653</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="F33" s="2">
         <v>3</v>
@@ -7771,24 +7747,24 @@
         <v>69</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>63</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="F34" s="2">
         <v>4</v>
@@ -7809,7 +7785,7 @@
         <v>69</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7817,16 +7793,16 @@
         <v>452</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="F35" s="2">
         <v>5</v>
@@ -7847,7 +7823,7 @@
         <v>69</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7855,16 +7831,16 @@
         <v>472</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="F36" s="2">
         <v>5</v>
@@ -7885,7 +7861,7 @@
         <v>69</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7893,16 +7869,16 @@
         <v>497</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="F37" s="2">
         <v>3</v>
@@ -7923,7 +7899,7 @@
         <v>69</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7931,16 +7907,16 @@
         <v>514</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
       <c r="F38" s="2">
         <v>3</v>
@@ -7961,7 +7937,7 @@
         <v>69</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -7996,13 +7972,13 @@
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>666</v>
@@ -8011,22 +7987,22 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1593</v>
+        <v>1585</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1433</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8055,10 +8031,10 @@
         <v>689</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>1437</v>
@@ -8096,7 +8072,7 @@
         <v>701</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
@@ -8135,7 +8111,7 @@
         <v>701</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
@@ -8174,7 +8150,7 @@
         <v>701</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
@@ -8213,7 +8189,7 @@
         <v>701</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
@@ -8252,7 +8228,7 @@
         <v>701</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -8291,10 +8267,10 @@
         <v>689</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>1437</v>
@@ -8332,10 +8308,10 @@
         <v>689</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>1437</v>
@@ -8373,10 +8349,10 @@
         <v>689</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>1437</v>
@@ -8414,10 +8390,10 @@
         <v>689</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>1437</v>
@@ -8455,10 +8431,10 @@
         <v>689</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>1437</v>
@@ -8496,10 +8472,10 @@
         <v>689</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>1437</v>
@@ -8537,7 +8513,7 @@
         <v>701</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -8576,7 +8552,7 @@
         <v>701</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
@@ -8615,7 +8591,7 @@
         <v>701</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -8654,10 +8630,10 @@
         <v>689</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>1437</v>
@@ -8695,10 +8671,10 @@
         <v>689</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1620</v>
+        <v>1612</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>1437</v>
@@ -8736,7 +8712,7 @@
         <v>701</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1621</v>
+        <v>1613</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
@@ -8775,7 +8751,7 @@
         <v>701</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
@@ -8814,10 +8790,10 @@
         <v>689</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>1437</v>
@@ -8855,7 +8831,7 @@
         <v>701</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
@@ -8894,10 +8870,10 @@
         <v>689</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1626</v>
+        <v>1618</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1627</v>
+        <v>1619</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>1437</v>
@@ -8935,10 +8911,10 @@
         <v>689</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1629</v>
+        <v>1621</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>1437</v>
@@ -8976,10 +8952,10 @@
         <v>689</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1630</v>
+        <v>1622</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>1437</v>
@@ -9017,10 +8993,10 @@
         <v>689</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>1437</v>
@@ -9058,10 +9034,10 @@
         <v>689</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1634</v>
+        <v>1626</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1635</v>
+        <v>1627</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>1437</v>
@@ -9099,10 +9075,10 @@
         <v>689</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1637</v>
+        <v>1629</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>1437</v>
@@ -9140,10 +9116,10 @@
         <v>689</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>1437</v>
@@ -9181,7 +9157,7 @@
         <v>701</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
@@ -9220,7 +9196,7 @@
         <v>701</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1641</v>
+        <v>1633</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
@@ -9259,10 +9235,10 @@
         <v>689</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1643</v>
+        <v>1635</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>1437</v>
@@ -9300,7 +9276,7 @@
         <v>701</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
@@ -9339,10 +9315,10 @@
         <v>689</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1645</v>
+        <v>1637</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>1437</v>
@@ -9380,10 +9356,10 @@
         <v>689</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>1437</v>
@@ -9421,7 +9397,7 @@
         <v>701</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1649</v>
+        <v>1641</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -9460,7 +9436,7 @@
         <v>701</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1650</v>
+        <v>1642</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
@@ -9499,7 +9475,7 @@
         <v>701</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1651</v>
+        <v>1643</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -9538,7 +9514,7 @@
         <v>701</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
@@ -9577,10 +9553,10 @@
         <v>689</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1653</v>
+        <v>1645</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>1437</v>
@@ -9618,10 +9594,10 @@
         <v>689</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>1437</v>
@@ -9659,10 +9635,10 @@
         <v>689</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1657</v>
+        <v>1649</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>1658</v>
+        <v>1650</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>1437</v>
@@ -9700,10 +9676,10 @@
         <v>689</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1659</v>
+        <v>1651</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>1660</v>
+        <v>1652</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>1437</v>
@@ -9741,7 +9717,7 @@
         <v>701</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1661</v>
+        <v>1653</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -9780,7 +9756,7 @@
         <v>701</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1662</v>
+        <v>1654</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
@@ -9819,7 +9795,7 @@
         <v>701</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
@@ -9858,7 +9834,7 @@
         <v>701</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
@@ -9897,7 +9873,7 @@
         <v>701</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1665</v>
+        <v>1657</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
@@ -9936,10 +9912,10 @@
         <v>689</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>1437</v>
@@ -9977,10 +9953,10 @@
         <v>689</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1669</v>
+        <v>1661</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1437</v>
@@ -10018,7 +9994,7 @@
         <v>701</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1670</v>
+        <v>1662</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
@@ -10057,10 +10033,10 @@
         <v>689</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>1672</v>
+        <v>1664</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>1437</v>
@@ -10098,7 +10074,7 @@
         <v>701</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1673</v>
+        <v>1665</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -10137,7 +10113,7 @@
         <v>701</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1674</v>
+        <v>1666</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -10176,7 +10152,7 @@
         <v>701</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1675</v>
+        <v>1667</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -10215,7 +10191,7 @@
         <v>701</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1676</v>
+        <v>1668</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -10254,10 +10230,10 @@
         <v>689</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1678</v>
+        <v>1670</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>1437</v>
@@ -10295,10 +10271,10 @@
         <v>689</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1679</v>
+        <v>1671</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1680</v>
+        <v>1672</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>1437</v>
@@ -10336,10 +10312,10 @@
         <v>689</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1681</v>
+        <v>1673</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>1437</v>
@@ -10377,7 +10353,7 @@
         <v>701</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1683</v>
+        <v>1675</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
@@ -10416,7 +10392,7 @@
         <v>701</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1684</v>
+        <v>1676</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
@@ -10455,16 +10431,16 @@
         <v>689</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1685</v>
+        <v>1677</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>1686</v>
+        <v>1678</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>1453</v>
+        <v>69</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>69</v>
@@ -10496,10 +10472,10 @@
         <v>689</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>1437</v>
@@ -10537,10 +10513,10 @@
         <v>689</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>1437</v>
@@ -10578,7 +10554,7 @@
         <v>701</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1690</v>
+        <v>1682</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
@@ -10617,10 +10593,10 @@
         <v>689</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1691</v>
+        <v>1683</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>1692</v>
+        <v>1684</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>1437</v>
@@ -10658,10 +10634,10 @@
         <v>689</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1693</v>
+        <v>1685</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>1692</v>
+        <v>1684</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>1437</v>
@@ -10699,10 +10675,10 @@
         <v>689</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>1694</v>
+        <v>1686</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>1692</v>
+        <v>1684</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>1437</v>
@@ -10740,10 +10716,10 @@
         <v>689</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1695</v>
+        <v>1687</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>1696</v>
+        <v>1688</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>1437</v>
@@ -10781,7 +10757,7 @@
         <v>701</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1697</v>
+        <v>1689</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
@@ -10820,7 +10796,7 @@
         <v>701</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1698</v>
+        <v>1690</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
@@ -10859,10 +10835,10 @@
         <v>689</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1699</v>
+        <v>1691</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>1700</v>
+        <v>1692</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>1437</v>
@@ -10900,10 +10876,10 @@
         <v>689</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1701</v>
+        <v>1693</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>1702</v>
+        <v>1694</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>1437</v>
@@ -10941,10 +10917,10 @@
         <v>689</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1703</v>
+        <v>1695</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1704</v>
+        <v>1696</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>1437</v>
@@ -10982,7 +10958,7 @@
         <v>701</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
@@ -11021,7 +10997,7 @@
         <v>701</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>1706</v>
+        <v>1698</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
@@ -11060,7 +11036,7 @@
         <v>701</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>1707</v>
+        <v>1699</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
@@ -11099,10 +11075,10 @@
         <v>689</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1708</v>
+        <v>1700</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>1709</v>
+        <v>1701</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>1437</v>
@@ -11140,10 +11116,10 @@
         <v>689</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1710</v>
+        <v>1702</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>1711</v>
+        <v>1703</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>1437</v>
@@ -11181,7 +11157,7 @@
         <v>701</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1712</v>
+        <v>1704</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
@@ -11220,10 +11196,10 @@
         <v>689</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1713</v>
+        <v>1705</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1714</v>
+        <v>1706</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1437</v>
@@ -11261,7 +11237,7 @@
         <v>701</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1715</v>
+        <v>1707</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
@@ -11300,10 +11276,10 @@
         <v>689</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>1716</v>
+        <v>1708</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>1717</v>
+        <v>1709</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>1437</v>
@@ -11341,7 +11317,7 @@
         <v>701</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>1718</v>
+        <v>1710</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -11380,7 +11356,7 @@
         <v>701</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -11419,7 +11395,7 @@
         <v>701</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>1720</v>
+        <v>1712</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
@@ -11458,10 +11434,10 @@
         <v>689</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1721</v>
+        <v>1713</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>1722</v>
+        <v>1714</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>1437</v>
@@ -11499,7 +11475,7 @@
         <v>701</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>1723</v>
+        <v>1715</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
@@ -11538,7 +11514,7 @@
         <v>701</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>1724</v>
+        <v>1716</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
@@ -11577,7 +11553,7 @@
         <v>701</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1725</v>
+        <v>1717</v>
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
@@ -11616,7 +11592,7 @@
         <v>701</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1726</v>
+        <v>1718</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
@@ -11655,7 +11631,7 @@
         <v>701</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>1727</v>
+        <v>1719</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
@@ -11694,10 +11670,10 @@
         <v>689</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1728</v>
+        <v>1720</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>1729</v>
+        <v>1721</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>1437</v>
@@ -11735,7 +11711,7 @@
         <v>701</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>1730</v>
+        <v>1722</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
@@ -11774,10 +11750,10 @@
         <v>689</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1731</v>
+        <v>1723</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>1732</v>
+        <v>1724</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>1437</v>
@@ -11815,7 +11791,7 @@
         <v>701</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>1733</v>
+        <v>1725</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
@@ -11854,7 +11830,7 @@
         <v>701</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1734</v>
+        <v>1726</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -11893,7 +11869,7 @@
         <v>701</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>1735</v>
+        <v>1727</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
@@ -11932,7 +11908,7 @@
         <v>701</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1736</v>
+        <v>1728</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -11971,7 +11947,7 @@
         <v>701</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>1737</v>
+        <v>1729</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
@@ -12010,7 +11986,7 @@
         <v>701</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1738</v>
+        <v>1730</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -12049,10 +12025,10 @@
         <v>689</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>1739</v>
+        <v>1731</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>1740</v>
+        <v>1732</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>1437</v>
@@ -12090,7 +12066,7 @@
         <v>701</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1741</v>
+        <v>1733</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
@@ -12129,7 +12105,7 @@
         <v>701</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2" t="s">
@@ -12168,7 +12144,7 @@
         <v>701</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>1743</v>
+        <v>1735</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -12207,10 +12183,10 @@
         <v>689</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1744</v>
+        <v>1736</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1745</v>
+        <v>1737</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>1437</v>
@@ -12248,10 +12224,10 @@
         <v>689</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1746</v>
+        <v>1738</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>1747</v>
+        <v>1739</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>1437</v>
@@ -12289,10 +12265,10 @@
         <v>689</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1748</v>
+        <v>1740</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1747</v>
+        <v>1739</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>1437</v>
@@ -12330,10 +12306,10 @@
         <v>689</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1749</v>
+        <v>1741</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>1750</v>
+        <v>1742</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>1437</v>
@@ -12371,10 +12347,10 @@
         <v>689</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1751</v>
+        <v>1743</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>1752</v>
+        <v>1744</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>1437</v>
@@ -12412,10 +12388,10 @@
         <v>689</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1753</v>
+        <v>1745</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>1752</v>
+        <v>1744</v>
       </c>
       <c r="K111" s="2" t="s">
         <v>1437</v>
@@ -12453,10 +12429,10 @@
         <v>689</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>1754</v>
+        <v>1746</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>1752</v>
+        <v>1744</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>1437</v>
@@ -12494,10 +12470,10 @@
         <v>689</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1755</v>
+        <v>1747</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>1437</v>
@@ -12535,10 +12511,10 @@
         <v>689</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1757</v>
+        <v>1749</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
       <c r="K114" s="2" t="s">
         <v>1437</v>
@@ -12576,10 +12552,10 @@
         <v>689</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>1437</v>
@@ -12617,10 +12593,10 @@
         <v>689</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1759</v>
+        <v>1751</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>1437</v>
@@ -12658,10 +12634,10 @@
         <v>689</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1760</v>
+        <v>1752</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1761</v>
+        <v>1753</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1437</v>
@@ -12699,10 +12675,10 @@
         <v>689</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1762</v>
+        <v>1754</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>1761</v>
+        <v>1753</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>1437</v>
@@ -12740,10 +12716,10 @@
         <v>689</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>1763</v>
+        <v>1755</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>1761</v>
+        <v>1753</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>1437</v>
@@ -12781,10 +12757,10 @@
         <v>689</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1764</v>
+        <v>1756</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1761</v>
+        <v>1753</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>1437</v>
@@ -12822,10 +12798,10 @@
         <v>689</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1765</v>
+        <v>1757</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1766</v>
+        <v>1758</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>1437</v>
@@ -12863,10 +12839,10 @@
         <v>689</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1767</v>
+        <v>1759</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1766</v>
+        <v>1758</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>1437</v>
@@ -12904,7 +12880,7 @@
         <v>701</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>1768</v>
+        <v>1760</v>
       </c>
       <c r="J123" s="2"/>
       <c r="K123" s="2" t="s">
@@ -12943,7 +12919,7 @@
         <v>701</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>1769</v>
+        <v>1761</v>
       </c>
       <c r="J124" s="2"/>
       <c r="K124" s="2" t="s">
@@ -12982,10 +12958,10 @@
         <v>689</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>1770</v>
+        <v>1762</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>1771</v>
+        <v>1763</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>1437</v>
@@ -13023,10 +12999,10 @@
         <v>689</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>1772</v>
+        <v>1764</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>1771</v>
+        <v>1763</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>1437</v>
@@ -13064,10 +13040,10 @@
         <v>689</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>1773</v>
+        <v>1765</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>1774</v>
+        <v>1766</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>1437</v>
@@ -13105,10 +13081,10 @@
         <v>689</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>1775</v>
+        <v>1767</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>1776</v>
+        <v>1768</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>1437</v>
@@ -13146,10 +13122,10 @@
         <v>689</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>1777</v>
+        <v>1769</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>1778</v>
+        <v>1770</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>1437</v>
@@ -13187,10 +13163,10 @@
         <v>689</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>1779</v>
+        <v>1771</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>1778</v>
+        <v>1770</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>1437</v>
@@ -13228,10 +13204,10 @@
         <v>689</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>1780</v>
+        <v>1772</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>1781</v>
+        <v>1773</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>1437</v>
@@ -13269,10 +13245,10 @@
         <v>689</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>1782</v>
+        <v>1774</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>1783</v>
+        <v>1775</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>1437</v>
@@ -13310,10 +13286,10 @@
         <v>689</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>1784</v>
+        <v>1776</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>1785</v>
+        <v>1777</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>1437</v>
@@ -13351,7 +13327,7 @@
         <v>701</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>1786</v>
+        <v>1778</v>
       </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2" t="s">
@@ -13390,10 +13366,10 @@
         <v>689</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>1787</v>
+        <v>1779</v>
       </c>
       <c r="J135" s="2" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
       <c r="K135" s="2" t="s">
         <v>1437</v>
@@ -13431,10 +13407,10 @@
         <v>689</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>1789</v>
+        <v>1781</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>1790</v>
+        <v>1782</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>1437</v>
@@ -13472,10 +13448,10 @@
         <v>689</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>1791</v>
+        <v>1783</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>1790</v>
+        <v>1782</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>1437</v>
@@ -13513,7 +13489,7 @@
         <v>701</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>1792</v>
+        <v>1784</v>
       </c>
       <c r="J138" s="2"/>
       <c r="K138" s="2" t="s">
@@ -13552,10 +13528,10 @@
         <v>689</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>1793</v>
+        <v>1785</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>1794</v>
+        <v>1786</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>1437</v>
@@ -13593,7 +13569,7 @@
         <v>701</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>1795</v>
+        <v>1787</v>
       </c>
       <c r="J140" s="2"/>
       <c r="K140" s="2" t="s">
@@ -13632,10 +13608,10 @@
         <v>689</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>1796</v>
+        <v>1788</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>1797</v>
+        <v>1789</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>1437</v>
@@ -13673,10 +13649,10 @@
         <v>689</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>1798</v>
+        <v>1790</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>1799</v>
+        <v>1791</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>1437</v>
@@ -13714,10 +13690,10 @@
         <v>689</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>1800</v>
+        <v>1792</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>1801</v>
+        <v>1793</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>1437</v>
@@ -13755,10 +13731,10 @@
         <v>689</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>1802</v>
+        <v>1794</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>1803</v>
+        <v>1795</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>1437</v>
@@ -13796,10 +13772,10 @@
         <v>689</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>1804</v>
+        <v>1796</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>1805</v>
+        <v>1797</v>
       </c>
       <c r="K145" s="2" t="s">
         <v>1437</v>
@@ -13835,40 +13811,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1805</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>1806</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>1807</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1808</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1809</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1810</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1811</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1812</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1813</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1814</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1815</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1435</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1816</v>
+        <v>1808</v>
       </c>
     </row>
   </sheetData>
@@ -13891,53 +13867,53 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1817</v>
+        <v>1809</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1818</v>
+        <v>1810</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1819</v>
+        <v>1811</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1810</v>
+        <v>1802</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1820</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1821</v>
+        <v>1813</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1822</v>
+        <v>1814</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1823</v>
+        <v>1815</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1824</v>
+        <v>1816</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1825</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1826</v>
+        <v>1818</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1822</v>
+        <v>1814</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1827</v>
+        <v>1819</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1828</v>
+        <v>1820</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1829</v>
+        <v>1821</v>
       </c>
     </row>
   </sheetData>
@@ -13960,206 +13936,206 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1830</v>
+        <v>1822</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>666</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1831</v>
+        <v>1823</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1832</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1833</v>
+        <v>1825</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1834</v>
+        <v>1826</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1835</v>
+        <v>1827</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1836</v>
+        <v>1828</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1837</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1838</v>
+        <v>1830</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1839</v>
+        <v>1831</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1840</v>
+        <v>1832</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1843</v>
+        <v>1835</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1844</v>
+        <v>1836</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1845</v>
+        <v>1837</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1846</v>
+        <v>1838</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1847</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1848</v>
+        <v>1840</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1849</v>
+        <v>1841</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1850</v>
+        <v>1842</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1851</v>
+        <v>1843</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1852</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1853</v>
+        <v>1845</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1854</v>
+        <v>1846</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1855</v>
+        <v>1847</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1856</v>
+        <v>1848</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1857</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1859</v>
+        <v>1851</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1860</v>
+        <v>1852</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1861</v>
+        <v>1853</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1862</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1863</v>
+        <v>1855</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1864</v>
+        <v>1856</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1865</v>
+        <v>1857</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1866</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1867</v>
+        <v>1859</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1868</v>
+        <v>1860</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1869</v>
+        <v>1861</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1870</v>
+        <v>1862</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1871</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1872</v>
+        <v>1864</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1873</v>
+        <v>1865</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1874</v>
+        <v>1866</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1875</v>
+        <v>1867</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1876</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1877</v>
+        <v>1869</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1878</v>
+        <v>1870</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1879</v>
+        <v>1871</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1880</v>
+        <v>1872</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1881</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1882</v>
+        <v>1874</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1883</v>
+        <v>1875</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1884</v>
+        <v>1876</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1885</v>
+        <v>1877</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1886</v>
+        <v>1878</v>
       </c>
     </row>
   </sheetData>
@@ -14182,186 +14158,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1887</v>
+        <v>1879</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1888</v>
+        <v>1880</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1889</v>
+        <v>1881</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1890</v>
+        <v>1882</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1891</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1892</v>
+        <v>1884</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1893</v>
+        <v>1885</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1895</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1896</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1897</v>
+        <v>1889</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1848</v>
+        <v>1840</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1898</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1899</v>
+        <v>1891</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1900</v>
+        <v>1892</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1901</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1902</v>
+        <v>1894</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1903</v>
+        <v>1895</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1904</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1905</v>
+        <v>1897</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1906</v>
+        <v>1898</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1907</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1908</v>
+        <v>1900</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1909</v>
+        <v>1901</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1910</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1911</v>
+        <v>1903</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1912</v>
+        <v>1904</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1913</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1914</v>
+        <v>1906</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1915</v>
+        <v>1907</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1916</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1917</v>
+        <v>1909</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1918</v>
+        <v>1910</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1919</v>
+        <v>1911</v>
       </c>
     </row>
   </sheetData>
@@ -26796,7 +26772,7 @@
         <v>1437</v>
       </c>
       <c r="E2" s="2">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -26920,7 +26896,7 @@
         <v>1437</v>
       </c>
       <c r="E8" s="2">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -26939,7 +26915,7 @@
         <v>1437</v>
       </c>
       <c r="E9" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -26958,7 +26934,7 @@
         <v>1437</v>
       </c>
       <c r="E10" s="2">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -26996,7 +26972,7 @@
         <v>1437</v>
       </c>
       <c r="E12" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -27015,7 +26991,7 @@
         <v>1437</v>
       </c>
       <c r="E13" s="2">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -27097,7 +27073,7 @@
         <v>1437</v>
       </c>
       <c r="E17" s="2">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -27116,7 +27092,7 @@
         <v>1437</v>
       </c>
       <c r="E18" s="2">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -27177,7 +27153,7 @@
         <v>1437</v>
       </c>
       <c r="E21" s="2">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -27217,7 +27193,7 @@
         <v>1437</v>
       </c>
       <c r="E23" s="2">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -27236,7 +27212,7 @@
         <v>1437</v>
       </c>
       <c r="E24" s="2">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -27255,7 +27231,7 @@
         <v>1437</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -27274,7 +27250,7 @@
         <v>1437</v>
       </c>
       <c r="E26" s="2">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -27293,7 +27269,7 @@
         <v>1437</v>
       </c>
       <c r="E27" s="2">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -27312,7 +27288,7 @@
         <v>1437</v>
       </c>
       <c r="E28" s="2">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -27331,7 +27307,7 @@
         <v>1437</v>
       </c>
       <c r="E29" s="2">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -27392,7 +27368,7 @@
         <v>1437</v>
       </c>
       <c r="E32" s="2">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -27432,7 +27408,7 @@
         <v>1437</v>
       </c>
       <c r="E34" s="2">
-        <v>121</v>
+        <v>256</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -27451,7 +27427,7 @@
         <v>1437</v>
       </c>
       <c r="E35" s="2">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -27554,7 +27530,7 @@
         <v>1437</v>
       </c>
       <c r="E40" s="2">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -27573,7 +27549,7 @@
         <v>1437</v>
       </c>
       <c r="E41" s="2">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -27592,7 +27568,7 @@
         <v>1437</v>
       </c>
       <c r="E42" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -27611,7 +27587,7 @@
         <v>1437</v>
       </c>
       <c r="E43" s="2">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -27735,7 +27711,7 @@
         <v>1437</v>
       </c>
       <c r="E49" s="2">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -27754,7 +27730,7 @@
         <v>1437</v>
       </c>
       <c r="E50" s="2">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -27794,7 +27770,7 @@
         <v>1437</v>
       </c>
       <c r="E52" s="2">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -27897,7 +27873,7 @@
         <v>1437</v>
       </c>
       <c r="E57" s="2">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -27916,7 +27892,7 @@
         <v>1437</v>
       </c>
       <c r="E58" s="2">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -27935,7 +27911,7 @@
         <v>1437</v>
       </c>
       <c r="E59" s="2">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -27993,10 +27969,10 @@
         <v>996</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E62" s="2">
-        <v>30029</v>
+        <v>377</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -28015,7 +27991,7 @@
         <v>1437</v>
       </c>
       <c r="E63" s="2">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -28034,7 +28010,7 @@
         <v>1437</v>
       </c>
       <c r="E64" s="2">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -28074,7 +28050,7 @@
         <v>1437</v>
       </c>
       <c r="E66" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -28093,7 +28069,7 @@
         <v>1437</v>
       </c>
       <c r="E67" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -28112,7 +28088,7 @@
         <v>1437</v>
       </c>
       <c r="E68" s="2">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -28131,7 +28107,7 @@
         <v>1437</v>
       </c>
       <c r="E69" s="2">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -28192,7 +28168,7 @@
         <v>1437</v>
       </c>
       <c r="E72" s="2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -28211,7 +28187,7 @@
         <v>1437</v>
       </c>
       <c r="E73" s="2">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -28230,7 +28206,7 @@
         <v>1437</v>
       </c>
       <c r="E74" s="2">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -28312,7 +28288,7 @@
         <v>1437</v>
       </c>
       <c r="E78" s="2">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -28331,7 +28307,7 @@
         <v>1437</v>
       </c>
       <c r="E79" s="2">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -28371,7 +28347,7 @@
         <v>1437</v>
       </c>
       <c r="E81" s="2">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -28411,7 +28387,7 @@
         <v>1437</v>
       </c>
       <c r="E83" s="2">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -28493,7 +28469,7 @@
         <v>1437</v>
       </c>
       <c r="E87" s="2">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -28617,7 +28593,7 @@
         <v>1437</v>
       </c>
       <c r="E93" s="2">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -28657,7 +28633,7 @@
         <v>1437</v>
       </c>
       <c r="E95" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -28802,7 +28778,7 @@
         <v>1437</v>
       </c>
       <c r="E102" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -28884,7 +28860,7 @@
         <v>1437</v>
       </c>
       <c r="E106" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -28903,7 +28879,7 @@
         <v>1437</v>
       </c>
       <c r="E107" s="2">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -28922,7 +28898,7 @@
         <v>1437</v>
       </c>
       <c r="E108" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -28941,7 +28917,7 @@
         <v>1437</v>
       </c>
       <c r="E109" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -28979,7 +28955,7 @@
         <v>1437</v>
       </c>
       <c r="E111" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -28998,7 +28974,7 @@
         <v>1437</v>
       </c>
       <c r="E112" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -29017,7 +28993,7 @@
         <v>1437</v>
       </c>
       <c r="E113" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -29036,7 +29012,7 @@
         <v>1437</v>
       </c>
       <c r="E114" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -29055,7 +29031,7 @@
         <v>1437</v>
       </c>
       <c r="E115" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -29074,7 +29050,7 @@
         <v>1437</v>
       </c>
       <c r="E116" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -29093,7 +29069,7 @@
         <v>1437</v>
       </c>
       <c r="E117" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -29131,7 +29107,7 @@
         <v>1437</v>
       </c>
       <c r="E119" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -29169,7 +29145,7 @@
         <v>1437</v>
       </c>
       <c r="E121" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -29188,7 +29164,7 @@
         <v>1437</v>
       </c>
       <c r="E122" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -29249,7 +29225,7 @@
         <v>1437</v>
       </c>
       <c r="E125" s="2">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -29268,7 +29244,7 @@
         <v>1437</v>
       </c>
       <c r="E126" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -29287,7 +29263,7 @@
         <v>1437</v>
       </c>
       <c r="E127" s="2">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -29306,7 +29282,7 @@
         <v>1437</v>
       </c>
       <c r="E128" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -29344,7 +29320,7 @@
         <v>1437</v>
       </c>
       <c r="E130" s="2">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -29363,7 +29339,7 @@
         <v>1437</v>
       </c>
       <c r="E131" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
@@ -29382,7 +29358,7 @@
         <v>1437</v>
       </c>
       <c r="E132" s="2">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -29401,7 +29377,7 @@
         <v>1437</v>
       </c>
       <c r="E133" s="2">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
@@ -29441,7 +29417,7 @@
         <v>1437</v>
       </c>
       <c r="E135" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -29460,7 +29436,7 @@
         <v>1437</v>
       </c>
       <c r="E136" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
@@ -29479,7 +29455,7 @@
         <v>1437</v>
       </c>
       <c r="E137" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
@@ -29519,7 +29495,7 @@
         <v>1437</v>
       </c>
       <c r="E139" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
@@ -29559,7 +29535,7 @@
         <v>1437</v>
       </c>
       <c r="E141" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -29578,7 +29554,7 @@
         <v>1437</v>
       </c>
       <c r="E142" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -29597,7 +29573,7 @@
         <v>1437</v>
       </c>
       <c r="E143" s="2">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -29616,7 +29592,7 @@
         <v>1437</v>
       </c>
       <c r="E144" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -29635,7 +29611,7 @@
         <v>1437</v>
       </c>
       <c r="E145" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
@@ -29648,7 +29624,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -29669,16 +29645,16 @@
         <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1443</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1444</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1432</v>
@@ -29687,68 +29663,29 @@
         <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>1448</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>1449</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>1450</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>1452</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1453</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1454</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>1456</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>1457</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29773,19 +29710,19 @@
         <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1432</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1433</v>
@@ -29794,96 +29731,96 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>623</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1468</v>
+        <v>1462</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>640</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1470</v>
+        <v>1464</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>653</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1474</v>
+        <v>1468</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>303</v>
@@ -29892,27 +29829,27 @@
         <v>1214</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>374</v>
@@ -29921,27 +29858,27 @@
         <v>1233</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1478</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1479</v>
+        <v>1473</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1480</v>
+        <v>1474</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>150</v>
@@ -29950,19 +29887,19 @@
         <v>1286</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>1437</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
     </row>
   </sheetData>
@@ -29989,16 +29926,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1482</v>
+        <v>1476</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1483</v>
+        <v>1477</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>689</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1484</v>
+        <v>1478</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -30027,7 +29964,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30050,7 +29987,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30073,7 +30010,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30096,7 +30033,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30119,7 +30056,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30142,7 +30079,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30165,7 +30102,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30188,7 +30125,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30211,7 +30148,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30234,7 +30171,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30257,7 +30194,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30280,7 +30217,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30303,7 +30240,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30326,7 +30263,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30349,7 +30286,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30372,7 +30309,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30395,7 +30332,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30418,7 +30355,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30441,7 +30378,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30464,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30487,7 +30424,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30510,7 +30447,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30533,7 +30470,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30556,7 +30493,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30579,7 +30516,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30602,7 +30539,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30625,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30648,7 +30585,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30671,7 +30608,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30694,7 +30631,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30717,7 +30654,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30740,7 +30677,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30763,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30786,7 +30723,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30809,7 +30746,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30832,7 +30769,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30855,7 +30792,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30878,7 +30815,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30901,7 +30838,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30924,7 +30861,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30947,7 +30884,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30970,7 +30907,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -30993,7 +30930,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31016,7 +30953,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31039,7 +30976,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31062,7 +30999,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31085,7 +31022,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31108,7 +31045,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31131,7 +31068,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31154,7 +31091,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31177,7 +31114,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31200,7 +31137,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31223,7 +31160,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31246,7 +31183,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31269,7 +31206,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31292,7 +31229,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31315,7 +31252,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31338,7 +31275,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31361,7 +31298,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31384,7 +31321,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31407,7 +31344,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31430,7 +31367,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31453,7 +31390,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31476,7 +31413,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31499,7 +31436,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31522,7 +31459,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31542,10 +31479,10 @@
         <v>1</v>
       </c>
       <c r="F68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31568,7 +31505,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31591,7 +31528,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31614,7 +31551,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31637,7 +31574,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31660,7 +31597,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31683,7 +31620,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31706,7 +31643,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31729,7 +31666,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31752,7 +31689,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31775,7 +31712,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31798,7 +31735,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31821,7 +31758,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31844,7 +31781,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31867,7 +31804,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31890,7 +31827,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31913,7 +31850,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31936,7 +31873,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31959,7 +31896,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -31982,7 +31919,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32005,7 +31942,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32028,7 +31965,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32051,7 +31988,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32074,7 +32011,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32097,7 +32034,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32120,7 +32057,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32143,7 +32080,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32166,7 +32103,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32189,7 +32126,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32212,7 +32149,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32235,7 +32172,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32258,7 +32195,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32281,7 +32218,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32304,7 +32241,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32327,7 +32264,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32350,7 +32287,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32373,7 +32310,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32396,7 +32333,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32419,7 +32356,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32442,7 +32379,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32465,7 +32402,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32488,7 +32425,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1485</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32511,7 +32448,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32534,7 +32471,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32557,7 +32494,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32580,7 +32517,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32603,7 +32540,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32626,7 +32563,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32649,7 +32586,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32672,7 +32609,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32695,7 +32632,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32718,7 +32655,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32741,7 +32678,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32764,7 +32701,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32787,7 +32724,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32810,7 +32747,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32833,7 +32770,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32856,7 +32793,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32879,7 +32816,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32902,7 +32839,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32925,7 +32862,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32948,7 +32885,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="130" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32971,7 +32908,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="131" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -32994,7 +32931,7 @@
         <v>0</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="132" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33017,7 +32954,7 @@
         <v>0</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="133" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33040,7 +32977,7 @@
         <v>0</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="134" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33063,7 +33000,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="135" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33086,7 +33023,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="136" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33109,7 +33046,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="137" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33132,7 +33069,7 @@
         <v>0</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="138" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33155,7 +33092,7 @@
         <v>0</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="139" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -33178,7 +33115,7 @@
         <v>0</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
     </row>
   </sheetData>
@@ -33200,13 +33137,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1489</v>
+        <v>1482</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1491</v>
+        <v>1484</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -33214,212 +33151,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1492</v>
+        <v>1485</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1493</v>
+        <v>1486</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1494</v>
+        <v>1487</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1496</v>
+        <v>1489</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1497</v>
+        <v>1490</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1498</v>
+        <v>1491</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1499</v>
+        <v>1492</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1500</v>
+        <v>1493</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1501</v>
+        <v>1494</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1502</v>
+        <v>1495</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1503</v>
+        <v>1496</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1504</v>
+        <v>1497</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1505</v>
+        <v>1498</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1506</v>
+        <v>1499</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1507</v>
+        <v>1500</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1508</v>
+        <v>1501</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1509</v>
+        <v>1502</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1280</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1510</v>
+        <v>1503</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1511</v>
+        <v>1504</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1512</v>
+        <v>1505</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1513</v>
+        <v>1506</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1514</v>
+        <v>1507</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1515</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1516</v>
+        <v>1509</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1517</v>
+        <v>1510</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1518</v>
+        <v>1511</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1519</v>
+        <v>1512</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1520</v>
+        <v>1513</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1521</v>
+        <v>1514</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1522</v>
+        <v>1515</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1523</v>
+        <v>1516</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>928</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1524</v>
+        <v>1517</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1527</v>
+        <v>1520</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1528</v>
+        <v>1521</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1529</v>
+        <v>1522</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1530</v>
+        <v>1523</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1531</v>
+        <v>1524</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>980</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1532</v>
+        <v>1525</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1533</v>
+        <v>1526</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1515</v>
+        <v>1508</v>
       </c>
     </row>
   </sheetData>
